--- a/Matricula_4to_grado.xlsx
+++ b/Matricula_4to_grado.xlsx
@@ -1,25 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="21727"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Escuela Juana R\Desktop\año escolar 2025-2026 matricula\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E73439-EC39-4C93-92DD-5EA656F87561}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="20490" windowHeight="7530" tabRatio="278"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="278" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -419,8 +419,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="10">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -489,6 +489,13 @@
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -510,7 +517,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="14">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -614,15 +621,6 @@
     </border>
     <border>
       <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right/>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
         <color indexed="64"/>
       </left>
       <right/>
@@ -673,7 +671,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
@@ -695,13 +693,7 @@
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
@@ -739,88 +731,113 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -858,7 +875,7 @@
         <xdr:cNvPr id="2" name="Image 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{00000000-0008-0000-0000-000002000000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1148,8 +1165,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A5:AE31"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A5:AE28"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="9" style="2"/>
@@ -1174,165 +1191,165 @@
   </cols>
   <sheetData>
     <row r="5" spans="1:31" ht="30.95" customHeight="1">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="57" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="35"/>
-      <c r="C5" s="35"/>
-      <c r="D5" s="35"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="35"/>
-      <c r="G5" s="35"/>
-      <c r="H5" s="35"/>
-      <c r="I5" s="35"/>
-      <c r="J5" s="35"/>
-      <c r="K5" s="35"/>
-      <c r="L5" s="35"/>
-      <c r="M5" s="35"/>
-      <c r="N5" s="35"/>
-      <c r="O5" s="35"/>
-      <c r="P5" s="35"/>
-      <c r="Q5" s="35"/>
-      <c r="R5" s="35"/>
-      <c r="S5" s="35"/>
-      <c r="T5" s="35"/>
-      <c r="U5" s="35"/>
-      <c r="V5" s="35"/>
-      <c r="W5" s="28"/>
-      <c r="X5" s="28"/>
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+      <c r="O5" s="58"/>
+      <c r="P5" s="58"/>
+      <c r="Q5" s="58"/>
+      <c r="R5" s="58"/>
+      <c r="S5" s="58"/>
+      <c r="T5" s="58"/>
+      <c r="U5" s="58"/>
+      <c r="V5" s="58"/>
+      <c r="W5" s="32"/>
+      <c r="X5" s="32"/>
       <c r="Y5" s="1"/>
-      <c r="Z5" s="28"/>
-      <c r="AA5" s="28"/>
-      <c r="AB5" s="28"/>
+      <c r="Z5" s="32"/>
+      <c r="AA5" s="32"/>
+      <c r="AB5" s="32"/>
       <c r="AC5" s="1"/>
-      <c r="AD5" s="28"/>
-      <c r="AE5" s="28"/>
+      <c r="AD5" s="32"/>
+      <c r="AE5" s="32"/>
     </row>
     <row r="6" spans="1:31" ht="27.95" customHeight="1">
-      <c r="A6" s="29" t="s">
+      <c r="A6" s="54" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29" t="s">
+      <c r="B6" s="55"/>
+      <c r="C6" s="54" t="s">
         <v>121</v>
       </c>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29" t="s">
+      <c r="D6" s="55"/>
+      <c r="E6" s="54" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29" t="s">
+      <c r="F6" s="56"/>
+      <c r="G6" s="56"/>
+      <c r="H6" s="55"/>
+      <c r="I6" s="54" t="s">
         <v>124</v>
       </c>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29" t="s">
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="55"/>
+      <c r="M6" s="54" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29" t="s">
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="55"/>
+      <c r="Q6" s="54" t="s">
         <v>36</v>
       </c>
-      <c r="R6" s="29"/>
-      <c r="S6" s="31" t="s">
+      <c r="R6" s="55"/>
+      <c r="S6" s="36" t="s">
         <v>128</v>
       </c>
-      <c r="T6" s="32"/>
-      <c r="U6" s="32"/>
-      <c r="V6" s="33"/>
-      <c r="W6" s="28"/>
-      <c r="X6" s="28"/>
-      <c r="Z6" s="30"/>
-      <c r="AA6" s="30"/>
-      <c r="AB6" s="30"/>
+      <c r="T6" s="37"/>
+      <c r="U6" s="37"/>
+      <c r="V6" s="38"/>
+      <c r="W6" s="32"/>
+      <c r="X6" s="32"/>
+      <c r="Z6" s="35"/>
+      <c r="AA6" s="35"/>
+      <c r="AB6" s="35"/>
       <c r="AC6" s="1"/>
-      <c r="AD6" s="30"/>
-      <c r="AE6" s="30"/>
+      <c r="AD6" s="35"/>
+      <c r="AE6" s="35"/>
     </row>
     <row r="7" spans="1:31" ht="36" customHeight="1">
-      <c r="A7" s="42" t="s">
+      <c r="A7" s="54" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="43"/>
-      <c r="C7" s="44"/>
-      <c r="D7" s="36" t="s">
+      <c r="B7" s="56"/>
+      <c r="C7" s="55"/>
+      <c r="D7" s="51" t="s">
         <v>0</v>
       </c>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36" t="s">
+      <c r="E7" s="53"/>
+      <c r="F7" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36" t="s">
+      <c r="G7" s="53"/>
+      <c r="H7" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="I7" s="36"/>
-      <c r="J7" s="36"/>
-      <c r="K7" s="42" t="s">
+      <c r="I7" s="52"/>
+      <c r="J7" s="53"/>
+      <c r="K7" s="54" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="44"/>
-      <c r="M7" s="36" t="s">
+      <c r="L7" s="55"/>
+      <c r="M7" s="51" t="s">
         <v>38</v>
       </c>
-      <c r="N7" s="36"/>
-      <c r="O7" s="36" t="s">
+      <c r="N7" s="53"/>
+      <c r="O7" s="51" t="s">
         <v>39</v>
       </c>
-      <c r="P7" s="36"/>
-      <c r="Q7" s="36"/>
-      <c r="R7" s="36"/>
-      <c r="S7" s="13" t="s">
+      <c r="P7" s="52"/>
+      <c r="Q7" s="52"/>
+      <c r="R7" s="53"/>
+      <c r="S7" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="T7" s="13" t="s">
+      <c r="T7" s="11" t="s">
         <v>40</v>
       </c>
-      <c r="U7" s="38" t="s">
+      <c r="U7" s="33" t="s">
         <v>41</v>
       </c>
-      <c r="V7" s="39"/>
+      <c r="V7" s="34"/>
       <c r="W7" s="3"/>
       <c r="AA7" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="AB7" s="28"/>
-      <c r="AC7" s="28"/>
-      <c r="AD7" s="28"/>
+      <c r="AB7" s="32"/>
+      <c r="AC7" s="32"/>
+      <c r="AD7" s="32"/>
       <c r="AE7" s="4"/>
     </row>
     <row r="8" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A8" s="37" t="s">
+      <c r="A8" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="37"/>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
-      <c r="F8" s="37"/>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
-      <c r="I8" s="37"/>
-      <c r="J8" s="37"/>
-      <c r="K8" s="37"/>
-      <c r="L8" s="37"/>
-      <c r="M8" s="37"/>
-      <c r="N8" s="37"/>
-      <c r="O8" s="37"/>
-      <c r="P8" s="37"/>
-      <c r="Q8" s="40" t="s">
+      <c r="B8" s="49"/>
+      <c r="C8" s="49"/>
+      <c r="D8" s="49"/>
+      <c r="E8" s="49"/>
+      <c r="F8" s="49"/>
+      <c r="G8" s="49"/>
+      <c r="H8" s="49"/>
+      <c r="I8" s="49"/>
+      <c r="J8" s="49"/>
+      <c r="K8" s="49"/>
+      <c r="L8" s="49"/>
+      <c r="M8" s="49"/>
+      <c r="N8" s="49"/>
+      <c r="O8" s="49"/>
+      <c r="P8" s="50"/>
+      <c r="Q8" s="48" t="s">
         <v>5</v>
       </c>
-      <c r="R8" s="41"/>
-      <c r="S8" s="41"/>
-      <c r="T8" s="41"/>
-      <c r="U8" s="41"/>
-      <c r="V8" s="41"/>
+      <c r="R8" s="49"/>
+      <c r="S8" s="49"/>
+      <c r="T8" s="49"/>
+      <c r="U8" s="49"/>
+      <c r="V8" s="49"/>
       <c r="W8" s="4"/>
       <c r="X8" s="1"/>
       <c r="Y8" s="1"/>
@@ -1344,67 +1361,67 @@
       <c r="AE8" s="4"/>
     </row>
     <row r="9" spans="1:31" ht="15">
-      <c r="A9" s="45" t="s">
+      <c r="A9" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="45" t="s">
+      <c r="B9" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="45" t="s">
+      <c r="D9" s="44" t="s">
         <v>9</v>
       </c>
       <c r="E9" s="45"/>
-      <c r="F9" s="45" t="s">
+      <c r="F9" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="45" t="s">
+      <c r="G9" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="45" t="s">
+      <c r="H9" s="41" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="45"/>
-      <c r="J9" s="45"/>
-      <c r="K9" s="45" t="s">
+      <c r="I9" s="42"/>
+      <c r="J9" s="43"/>
+      <c r="K9" s="30" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="45" t="s">
+      <c r="L9" s="41" t="s">
         <v>13</v>
       </c>
-      <c r="M9" s="45"/>
-      <c r="N9" s="45" t="s">
+      <c r="M9" s="43"/>
+      <c r="N9" s="41" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="45"/>
-      <c r="P9" s="45"/>
-      <c r="Q9" s="49" t="s">
+      <c r="O9" s="42"/>
+      <c r="P9" s="43"/>
+      <c r="Q9" s="26" t="s">
         <v>14</v>
       </c>
-      <c r="R9" s="50"/>
-      <c r="S9" s="45" t="s">
+      <c r="R9" s="27"/>
+      <c r="S9" s="30" t="s">
         <v>8</v>
       </c>
-      <c r="T9" s="45" t="s">
+      <c r="T9" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="45" t="s">
+      <c r="U9" s="30" t="s">
         <v>26</v>
       </c>
-      <c r="V9" s="48" t="s">
+      <c r="V9" s="39" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="10" spans="1:31" ht="15">
-      <c r="A10" s="45"/>
-      <c r="B10" s="45"/>
-      <c r="C10" s="47"/>
-      <c r="D10" s="45"/>
-      <c r="E10" s="45"/>
-      <c r="F10" s="45"/>
-      <c r="G10" s="45"/>
+      <c r="A10" s="31"/>
+      <c r="B10" s="31"/>
+      <c r="C10" s="31"/>
+      <c r="D10" s="46"/>
+      <c r="E10" s="47"/>
+      <c r="F10" s="31"/>
+      <c r="G10" s="31"/>
       <c r="H10" s="5" t="s">
         <v>15</v>
       </c>
@@ -1414,7 +1431,7 @@
       <c r="J10" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="45"/>
+      <c r="K10" s="31"/>
       <c r="L10" s="5" t="s">
         <v>18</v>
       </c>
@@ -1430,54 +1447,54 @@
       <c r="P10" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="Q10" s="51"/>
-      <c r="R10" s="52"/>
-      <c r="S10" s="45"/>
-      <c r="T10" s="45"/>
-      <c r="U10" s="45"/>
-      <c r="V10" s="48"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="29"/>
+      <c r="S10" s="31"/>
+      <c r="T10" s="31"/>
+      <c r="U10" s="31"/>
+      <c r="V10" s="40"/>
     </row>
     <row r="11" spans="1:31" ht="16.5">
       <c r="A11" s="6">
         <v>1</v>
       </c>
-      <c r="B11" s="12"/>
-      <c r="C11" s="15">
+      <c r="B11" s="10"/>
+      <c r="C11" s="13">
         <v>36825110</v>
       </c>
-      <c r="D11" s="18" t="s">
+      <c r="D11" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="18" t="s">
+      <c r="E11" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="15" t="s">
+      <c r="F11" s="13" t="s">
         <v>32</v>
       </c>
       <c r="G11" s="6"/>
-      <c r="H11" s="20">
+      <c r="H11" s="18">
         <v>8</v>
       </c>
-      <c r="I11" s="20">
+      <c r="I11" s="18">
         <v>2</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J11" s="19">
         <v>2015</v>
       </c>
-      <c r="K11" s="11" t="s">
+      <c r="K11" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L11" s="11" t="s">
+      <c r="L11" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M11" s="9"/>
-      <c r="N11" s="11">
+      <c r="M11" s="8"/>
+      <c r="N11" s="9">
         <v>10</v>
       </c>
-      <c r="O11" s="11">
+      <c r="O11" s="9">
         <v>10</v>
       </c>
-      <c r="P11" s="11">
+      <c r="P11" s="9">
         <v>36</v>
       </c>
       <c r="Q11" s="6" t="s">
@@ -1486,16 +1503,16 @@
       <c r="R11" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="S11" s="15">
+      <c r="S11" s="13">
         <v>25560232</v>
       </c>
-      <c r="T11" s="15">
+      <c r="T11" s="13">
         <v>4129743760</v>
       </c>
-      <c r="U11" s="15" t="s">
+      <c r="U11" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V11" s="19" t="s">
+      <c r="V11" s="17" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1503,42 +1520,42 @@
       <c r="A12" s="6">
         <v>2</v>
       </c>
-      <c r="C12" s="15">
+      <c r="C12" s="13">
         <v>36946904</v>
       </c>
-      <c r="D12" s="18" t="s">
+      <c r="D12" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="18" t="s">
+      <c r="E12" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="15" t="s">
+      <c r="F12" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G12" s="6"/>
-      <c r="H12" s="20">
+      <c r="H12" s="18">
         <v>6</v>
       </c>
-      <c r="I12" s="20">
+      <c r="I12" s="18">
         <v>2</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J12" s="19">
         <v>2016</v>
       </c>
-      <c r="K12" s="11" t="s">
+      <c r="K12" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L12" s="11" t="s">
+      <c r="L12" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M12" s="9"/>
-      <c r="N12" s="11">
+      <c r="M12" s="8"/>
+      <c r="N12" s="9">
         <v>12</v>
       </c>
-      <c r="O12" s="11">
+      <c r="O12" s="9">
         <v>12</v>
       </c>
-      <c r="P12" s="11">
+      <c r="P12" s="9">
         <v>35</v>
       </c>
       <c r="Q12" s="6" t="s">
@@ -1547,16 +1564,16 @@
       <c r="R12" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="S12" s="15">
+      <c r="S12" s="13">
         <v>19894172</v>
       </c>
-      <c r="T12" s="15">
+      <c r="T12" s="13">
         <v>4127932191</v>
       </c>
-      <c r="U12" s="15" t="s">
+      <c r="U12" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="V12" s="19" t="s">
+      <c r="V12" s="17" t="s">
         <v>54</v>
       </c>
     </row>
@@ -1565,42 +1582,42 @@
         <v>3</v>
       </c>
       <c r="B13" s="7"/>
-      <c r="C13" s="15">
+      <c r="C13" s="13">
         <v>37120471</v>
       </c>
-      <c r="D13" s="18" t="s">
+      <c r="D13" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="18" t="s">
+      <c r="E13" s="16" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F13" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G13" s="6"/>
-      <c r="H13" s="17">
+      <c r="H13" s="15">
         <v>1</v>
       </c>
-      <c r="I13" s="17">
+      <c r="I13" s="15">
         <v>9</v>
       </c>
-      <c r="J13" s="15">
+      <c r="J13" s="13">
         <v>2014</v>
       </c>
-      <c r="K13" s="15" t="s">
+      <c r="K13" s="13" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="14" t="s">
+      <c r="L13" s="12" t="s">
         <v>122</v>
       </c>
-      <c r="M13" s="9"/>
-      <c r="N13" s="11">
+      <c r="M13" s="8"/>
+      <c r="N13" s="9">
         <v>14</v>
       </c>
-      <c r="O13" s="11">
+      <c r="O13" s="9">
         <v>14</v>
       </c>
-      <c r="P13" s="11">
+      <c r="P13" s="9">
         <v>37</v>
       </c>
       <c r="Q13" s="6" t="s">
@@ -1609,16 +1626,16 @@
       <c r="R13" s="6" t="s">
         <v>53</v>
       </c>
-      <c r="S13" s="15">
+      <c r="S13" s="13">
         <v>22655608</v>
       </c>
-      <c r="T13" s="15">
+      <c r="T13" s="13">
         <v>4121338291</v>
       </c>
-      <c r="U13" s="15" t="s">
+      <c r="U13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V13" s="19" t="s">
+      <c r="V13" s="17" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1627,42 +1644,42 @@
         <v>4</v>
       </c>
       <c r="B14" s="7"/>
-      <c r="C14" s="15">
+      <c r="C14" s="13">
         <v>37302811</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F14" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G14" s="6"/>
-      <c r="H14" s="17">
+      <c r="H14" s="15">
         <v>9</v>
       </c>
-      <c r="I14" s="17">
+      <c r="I14" s="15">
         <v>10</v>
       </c>
-      <c r="J14" s="15">
+      <c r="J14" s="13">
         <v>2015</v>
       </c>
-      <c r="K14" s="11" t="s">
+      <c r="K14" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="11"/>
-      <c r="M14" s="11" t="s">
+      <c r="L14" s="9"/>
+      <c r="M14" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="N14" s="11">
+      <c r="N14" s="9">
         <v>12</v>
       </c>
-      <c r="O14" s="11">
+      <c r="O14" s="9">
         <v>12</v>
       </c>
-      <c r="P14" s="11">
+      <c r="P14" s="9">
         <v>35</v>
       </c>
       <c r="Q14" s="6" t="s">
@@ -1671,16 +1688,16 @@
       <c r="R14" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="S14" s="15">
+      <c r="S14" s="13">
         <v>19247972</v>
       </c>
-      <c r="T14" s="15">
+      <c r="T14" s="13">
         <v>4262178897</v>
       </c>
-      <c r="U14" s="15" t="s">
+      <c r="U14" s="13" t="s">
         <v>60</v>
       </c>
-      <c r="V14" s="19" t="s">
+      <c r="V14" s="17" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1689,42 +1706,42 @@
         <v>5</v>
       </c>
       <c r="B15" s="7"/>
-      <c r="C15" s="15">
+      <c r="C15" s="13">
         <v>37302842</v>
       </c>
-      <c r="D15" s="18" t="s">
+      <c r="D15" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="18" t="s">
+      <c r="E15" s="16" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F15" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G15" s="6"/>
-      <c r="H15" s="17">
+      <c r="H15" s="15">
         <v>15</v>
       </c>
-      <c r="I15" s="17">
+      <c r="I15" s="15">
         <v>6</v>
       </c>
-      <c r="J15" s="15">
+      <c r="J15" s="13">
         <v>2016</v>
       </c>
-      <c r="K15" s="11" t="s">
+      <c r="K15" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L15" s="11" t="s">
+      <c r="L15" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M15" s="9"/>
-      <c r="N15" s="11">
+      <c r="M15" s="8"/>
+      <c r="N15" s="9">
         <v>12</v>
       </c>
-      <c r="O15" s="11">
+      <c r="O15" s="9">
         <v>12</v>
       </c>
-      <c r="P15" s="11">
+      <c r="P15" s="9">
         <v>34</v>
       </c>
       <c r="Q15" s="6" t="s">
@@ -1733,16 +1750,16 @@
       <c r="R15" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="S15" s="15">
+      <c r="S15" s="13">
         <v>17521672</v>
       </c>
-      <c r="T15" s="15">
+      <c r="T15" s="13">
         <v>4122783453</v>
       </c>
-      <c r="U15" s="15" t="s">
+      <c r="U15" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="V15" s="19" t="s">
+      <c r="V15" s="17" t="s">
         <v>55</v>
       </c>
     </row>
@@ -1751,42 +1768,42 @@
         <v>6</v>
       </c>
       <c r="B16" s="7"/>
-      <c r="C16" s="15">
+      <c r="C16" s="13">
         <v>37375148</v>
       </c>
-      <c r="D16" s="18" t="s">
+      <c r="D16" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="18" t="s">
+      <c r="E16" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F16" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G16" s="6"/>
-      <c r="H16" s="17">
+      <c r="H16" s="15">
         <v>25</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I16" s="15">
         <v>7</v>
       </c>
-      <c r="J16" s="15">
+      <c r="J16" s="13">
         <v>2016</v>
       </c>
-      <c r="K16" s="11" t="s">
+      <c r="K16" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L16" s="11" t="s">
+      <c r="L16" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M16" s="9"/>
-      <c r="N16" s="11">
+      <c r="M16" s="8"/>
+      <c r="N16" s="9">
         <v>10</v>
       </c>
-      <c r="O16" s="11">
+      <c r="O16" s="9">
         <v>10</v>
       </c>
-      <c r="P16" s="11">
+      <c r="P16" s="9">
         <v>35</v>
       </c>
       <c r="Q16" s="6" t="s">
@@ -1795,60 +1812,60 @@
       <c r="R16" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="S16" s="15">
+      <c r="S16" s="13">
         <v>15756707</v>
       </c>
-      <c r="T16" s="15">
+      <c r="T16" s="13">
         <v>4262783746</v>
       </c>
-      <c r="U16" s="15" t="s">
+      <c r="U16" s="13" t="s">
         <v>66</v>
       </c>
-      <c r="V16" s="19" t="s">
+      <c r="V16" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="17" spans="1:22" ht="16.5">
+    <row r="17" spans="1:26" ht="16.5">
       <c r="A17" s="6">
         <v>7</v>
       </c>
-      <c r="B17" s="15">
+      <c r="B17" s="13">
         <v>11611954667</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="18" t="s">
+      <c r="C17" s="10"/>
+      <c r="D17" s="16" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="18" t="s">
+      <c r="E17" s="16" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="15" t="s">
+      <c r="F17" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G17" s="6"/>
-      <c r="H17" s="17">
+      <c r="H17" s="15">
         <v>29</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I17" s="15">
         <v>11</v>
       </c>
-      <c r="J17" s="15">
+      <c r="J17" s="13">
         <v>2016</v>
       </c>
-      <c r="K17" s="11" t="s">
+      <c r="K17" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L17" s="11" t="s">
+      <c r="L17" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M17" s="9"/>
-      <c r="N17" s="11">
+      <c r="M17" s="8"/>
+      <c r="N17" s="9">
         <v>12</v>
       </c>
-      <c r="O17" s="11">
+      <c r="O17" s="9">
         <v>12</v>
       </c>
-      <c r="P17" s="11">
+      <c r="P17" s="9">
         <v>34</v>
       </c>
       <c r="Q17" s="6" t="s">
@@ -1857,60 +1874,60 @@
       <c r="R17" s="6" t="s">
         <v>79</v>
       </c>
-      <c r="S17" s="15">
+      <c r="S17" s="13">
         <v>11954667</v>
       </c>
-      <c r="T17" s="15">
+      <c r="T17" s="13">
         <v>4127852674</v>
       </c>
-      <c r="U17" s="15" t="s">
+      <c r="U17" s="13" t="s">
         <v>65</v>
       </c>
-      <c r="V17" s="19" t="s">
+      <c r="V17" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="18" spans="1:22" ht="16.5">
+    <row r="18" spans="1:26" ht="16.5">
       <c r="A18" s="6">
         <v>8</v>
       </c>
-      <c r="B18" s="15">
+      <c r="B18" s="13">
         <v>11614588352</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="18" t="s">
+      <c r="C18" s="10"/>
+      <c r="D18" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="18" t="s">
+      <c r="E18" s="16" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="F18" s="13" t="s">
         <v>34</v>
       </c>
       <c r="G18" s="6"/>
-      <c r="H18" s="17">
+      <c r="H18" s="15">
         <v>31</v>
       </c>
-      <c r="I18" s="17">
+      <c r="I18" s="15">
         <v>12</v>
       </c>
-      <c r="J18" s="15">
+      <c r="J18" s="13">
         <v>2016</v>
       </c>
-      <c r="K18" s="11" t="s">
+      <c r="K18" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L18" s="11" t="s">
+      <c r="L18" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M18" s="9"/>
-      <c r="N18" s="11">
+      <c r="M18" s="8"/>
+      <c r="N18" s="9">
         <v>10</v>
       </c>
-      <c r="O18" s="11">
+      <c r="O18" s="9">
         <v>10</v>
       </c>
-      <c r="P18" s="11">
+      <c r="P18" s="9">
         <v>33</v>
       </c>
       <c r="Q18" s="6" t="s">
@@ -1919,60 +1936,60 @@
       <c r="R18" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="S18" s="15">
+      <c r="S18" s="13">
         <v>17522003</v>
       </c>
-      <c r="T18" s="15">
+      <c r="T18" s="13">
         <v>4122391903</v>
       </c>
-      <c r="U18" s="15" t="s">
+      <c r="U18" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="V18" s="19" t="s">
+      <c r="V18" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="19" spans="1:22" ht="16.5">
+    <row r="19" spans="1:26" ht="16.5">
       <c r="A19" s="6">
         <v>9</v>
       </c>
-      <c r="B19" s="15">
+      <c r="B19" s="13">
         <v>11616664117</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="18" t="s">
+      <c r="C19" s="10"/>
+      <c r="D19" s="16" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="18" t="s">
+      <c r="E19" s="16" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="F19" s="13" t="s">
         <v>32</v>
       </c>
       <c r="G19" s="6"/>
-      <c r="H19" s="17">
+      <c r="H19" s="15">
         <v>23</v>
       </c>
-      <c r="I19" s="17">
+      <c r="I19" s="15">
         <v>9</v>
       </c>
-      <c r="J19" s="15">
+      <c r="J19" s="13">
         <v>2016</v>
       </c>
-      <c r="K19" s="11" t="s">
+      <c r="K19" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L19" s="11" t="s">
+      <c r="L19" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M19" s="9"/>
-      <c r="N19" s="11">
+      <c r="M19" s="8"/>
+      <c r="N19" s="9">
         <v>10</v>
       </c>
-      <c r="O19" s="11">
+      <c r="O19" s="9">
         <v>8</v>
       </c>
-      <c r="P19" s="11">
+      <c r="P19" s="9">
         <v>35</v>
       </c>
       <c r="Q19" s="6" t="s">
@@ -1981,59 +1998,60 @@
       <c r="R19" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="S19" s="15">
+      <c r="S19" s="13">
         <v>16664117</v>
       </c>
-      <c r="T19" s="15">
+      <c r="T19" s="13">
         <v>4268144007</v>
       </c>
-      <c r="U19" s="15" t="s">
+      <c r="U19" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V19" s="19" t="s">
+      <c r="V19" s="17" t="s">
         <v>55</v>
       </c>
+      <c r="Z19" s="59"/>
     </row>
-    <row r="20" spans="1:22" ht="16.5">
+    <row r="20" spans="1:26" ht="16.5">
       <c r="A20" s="6">
         <v>10</v>
       </c>
-      <c r="B20" s="15">
+      <c r="B20" s="13">
         <v>11618965516</v>
       </c>
-      <c r="D20" s="16" t="s">
+      <c r="D20" s="14" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="16" t="s">
+      <c r="E20" s="14" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="14" t="s">
+      <c r="F20" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G20" s="6"/>
-      <c r="H20" s="17">
+      <c r="H20" s="15">
         <v>13</v>
       </c>
-      <c r="I20" s="17">
+      <c r="I20" s="15">
         <v>2</v>
       </c>
-      <c r="J20" s="15">
+      <c r="J20" s="13">
         <v>2017</v>
       </c>
-      <c r="K20" s="11" t="s">
+      <c r="K20" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L20" s="11" t="s">
+      <c r="L20" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M20" s="9"/>
-      <c r="N20" s="11">
+      <c r="M20" s="8"/>
+      <c r="N20" s="9">
         <v>10</v>
       </c>
-      <c r="O20" s="11">
+      <c r="O20" s="9">
         <v>10</v>
       </c>
-      <c r="P20" s="11">
+      <c r="P20" s="9">
         <v>33</v>
       </c>
       <c r="Q20" s="6" t="s">
@@ -2042,494 +2060,494 @@
       <c r="R20" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="S20" s="15">
+      <c r="S20" s="13">
         <v>18965516</v>
       </c>
-      <c r="T20" s="15">
+      <c r="T20" s="13">
         <v>4126878376</v>
       </c>
-      <c r="U20" s="14" t="s">
+      <c r="U20" s="12" t="s">
         <v>87</v>
       </c>
-      <c r="V20" s="19" t="s">
+      <c r="V20" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="21" spans="1:22" ht="16.5">
+    <row r="21" spans="1:26" ht="16.5">
       <c r="A21" s="6">
         <v>11</v>
       </c>
-      <c r="B21" s="15">
+      <c r="B21" s="13">
         <v>11619486274</v>
       </c>
       <c r="C21" s="7"/>
-      <c r="D21" s="16" t="s">
+      <c r="D21" s="14" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="16" t="s">
+      <c r="E21" s="14" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="14" t="s">
+      <c r="F21" s="12" t="s">
         <v>32</v>
       </c>
       <c r="G21" s="6"/>
-      <c r="H21" s="17">
+      <c r="H21" s="15">
         <v>13</v>
       </c>
-      <c r="I21" s="17">
+      <c r="I21" s="15">
         <v>12</v>
       </c>
-      <c r="J21" s="15">
+      <c r="J21" s="13">
         <v>2016</v>
       </c>
-      <c r="K21" s="11" t="s">
+      <c r="K21" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="11" t="s">
+      <c r="L21" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M21" s="9"/>
-      <c r="N21" s="11">
+      <c r="M21" s="8"/>
+      <c r="N21" s="9">
         <v>10</v>
       </c>
-      <c r="O21" s="11">
+      <c r="O21" s="9">
         <v>10</v>
       </c>
-      <c r="P21" s="11">
+      <c r="P21" s="9">
         <v>33</v>
       </c>
       <c r="Q21" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="R21" s="17" t="s">
+      <c r="R21" s="15" t="s">
         <v>105</v>
       </c>
-      <c r="S21" s="15">
+      <c r="S21" s="13">
         <v>19486274</v>
       </c>
-      <c r="T21" s="25">
+      <c r="T21" s="23">
         <v>4262370806</v>
       </c>
-      <c r="U21" s="15" t="s">
+      <c r="U21" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V21" s="19" t="s">
+      <c r="V21" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:22" ht="16.5">
+    <row r="22" spans="1:26" ht="16.5">
       <c r="A22" s="6">
         <v>12</v>
       </c>
-      <c r="B22" s="15">
+      <c r="B22" s="13">
         <v>11619486376</v>
       </c>
       <c r="C22" s="7"/>
-      <c r="D22" s="16" t="s">
+      <c r="D22" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="16" t="s">
+      <c r="E22" s="14" t="s">
         <v>91</v>
       </c>
-      <c r="F22" s="14" t="s">
+      <c r="F22" s="12" t="s">
         <v>32</v>
       </c>
       <c r="G22" s="6"/>
-      <c r="H22" s="17">
+      <c r="H22" s="15">
         <v>27</v>
       </c>
-      <c r="I22" s="17">
+      <c r="I22" s="15">
         <v>11</v>
       </c>
-      <c r="J22" s="15">
+      <c r="J22" s="13">
         <v>2016</v>
       </c>
-      <c r="K22" s="11" t="s">
+      <c r="K22" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L22" s="11" t="s">
+      <c r="L22" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M22" s="9"/>
-      <c r="N22" s="11">
+      <c r="M22" s="8"/>
+      <c r="N22" s="9">
         <v>12</v>
       </c>
-      <c r="O22" s="11">
+      <c r="O22" s="9">
         <v>12</v>
       </c>
-      <c r="P22" s="11">
+      <c r="P22" s="9">
         <v>33</v>
       </c>
       <c r="Q22" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="R22" s="17" t="s">
+      <c r="R22" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="S22" s="15">
+      <c r="S22" s="13">
         <v>19486376</v>
       </c>
-      <c r="T22" s="25">
+      <c r="T22" s="23">
         <v>4122496443</v>
       </c>
-      <c r="U22" s="15" t="s">
+      <c r="U22" s="13" t="s">
         <v>103</v>
       </c>
-      <c r="V22" s="19" t="s">
+      <c r="V22" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:22" ht="16.5">
+    <row r="23" spans="1:26" ht="16.5">
       <c r="A23" s="6">
         <v>13</v>
       </c>
-      <c r="B23" s="15">
+      <c r="B23" s="13">
         <v>11619892696</v>
       </c>
       <c r="C23" s="7"/>
-      <c r="D23" s="16" t="s">
+      <c r="D23" s="14" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="16" t="s">
+      <c r="E23" s="14" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="14" t="s">
+      <c r="F23" s="12" t="s">
         <v>32</v>
       </c>
       <c r="G23" s="6"/>
-      <c r="H23" s="17">
+      <c r="H23" s="15">
         <v>15</v>
       </c>
-      <c r="I23" s="17">
+      <c r="I23" s="15">
         <v>3</v>
       </c>
-      <c r="J23" s="15">
+      <c r="J23" s="13">
         <v>2016</v>
       </c>
-      <c r="K23" s="11" t="s">
+      <c r="K23" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L23" s="11" t="s">
+      <c r="L23" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M23" s="9"/>
-      <c r="N23" s="11">
+      <c r="M23" s="8"/>
+      <c r="N23" s="9">
         <v>12</v>
       </c>
-      <c r="O23" s="11">
+      <c r="O23" s="9">
         <v>12</v>
       </c>
-      <c r="P23" s="11">
+      <c r="P23" s="9">
         <v>35</v>
       </c>
       <c r="Q23" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="R23" s="17" t="s">
+      <c r="R23" s="15" t="s">
         <v>108</v>
       </c>
-      <c r="S23" s="15">
+      <c r="S23" s="13">
         <v>19892696</v>
       </c>
-      <c r="T23" s="15">
+      <c r="T23" s="13">
         <v>4121206878</v>
       </c>
-      <c r="U23" s="15" t="s">
+      <c r="U23" s="13" t="s">
         <v>104</v>
       </c>
-      <c r="V23" s="19" t="s">
+      <c r="V23" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:22" ht="16.5">
+    <row r="24" spans="1:26" ht="16.5">
       <c r="A24" s="6">
         <v>14</v>
       </c>
-      <c r="B24" s="15">
+      <c r="B24" s="13">
         <v>11620435077</v>
       </c>
       <c r="C24" s="7"/>
-      <c r="D24" s="16" t="s">
+      <c r="D24" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="16" t="s">
+      <c r="E24" s="14" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="14" t="s">
+      <c r="F24" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G24" s="6"/>
-      <c r="H24" s="17">
+      <c r="H24" s="15">
         <v>25</v>
       </c>
-      <c r="I24" s="23" t="s">
+      <c r="I24" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="J24" s="15">
+      <c r="J24" s="13">
         <v>2016</v>
       </c>
-      <c r="K24" s="11" t="s">
+      <c r="K24" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L24" s="11" t="s">
+      <c r="L24" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M24" s="9"/>
-      <c r="N24" s="11">
+      <c r="M24" s="8"/>
+      <c r="N24" s="9">
         <v>12</v>
       </c>
-      <c r="O24" s="11">
+      <c r="O24" s="9">
         <v>12</v>
       </c>
-      <c r="P24" s="11">
+      <c r="P24" s="9">
         <v>35</v>
       </c>
       <c r="Q24" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="R24" s="17" t="s">
+      <c r="R24" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="S24" s="15">
+      <c r="S24" s="13">
         <v>20435077</v>
       </c>
-      <c r="T24" s="15">
+      <c r="T24" s="13">
         <v>4127641205</v>
       </c>
-      <c r="U24" s="15" t="s">
+      <c r="U24" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V24" s="19" t="s">
+      <c r="V24" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="25" spans="1:22" ht="16.5">
+    <row r="25" spans="1:26" ht="16.5">
       <c r="A25" s="6">
         <v>15</v>
       </c>
-      <c r="B25" s="15">
+      <c r="B25" s="13">
         <v>11621121967</v>
       </c>
       <c r="C25" s="7"/>
-      <c r="D25" s="16" t="s">
+      <c r="D25" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="E25" s="16" t="s">
+      <c r="E25" s="14" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="14" t="s">
+      <c r="F25" s="12" t="s">
         <v>34</v>
       </c>
       <c r="G25" s="6"/>
-      <c r="H25" s="24">
+      <c r="H25" s="22">
         <v>22</v>
       </c>
-      <c r="I25" s="24">
+      <c r="I25" s="22">
         <v>10</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J25" s="20">
         <v>2016</v>
       </c>
-      <c r="K25" s="11" t="s">
+      <c r="K25" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L25" s="11" t="s">
+      <c r="L25" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M25" s="9"/>
-      <c r="N25" s="11">
+      <c r="M25" s="8"/>
+      <c r="N25" s="9">
         <v>8</v>
       </c>
-      <c r="O25" s="11">
+      <c r="O25" s="9">
         <v>8</v>
       </c>
-      <c r="P25" s="11">
+      <c r="P25" s="9">
         <v>35</v>
       </c>
       <c r="Q25" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="R25" s="17" t="s">
+      <c r="R25" s="15" t="s">
         <v>112</v>
       </c>
-      <c r="S25" s="15">
+      <c r="S25" s="13">
         <v>21121967</v>
       </c>
-      <c r="T25" s="15">
+      <c r="T25" s="13">
         <v>4164695815</v>
       </c>
-      <c r="U25" s="15" t="s">
+      <c r="U25" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V25" s="19" t="s">
+      <c r="V25" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="26" spans="1:22" ht="16.5">
+    <row r="26" spans="1:26" ht="16.5">
       <c r="A26" s="6">
         <v>16</v>
       </c>
-      <c r="B26" s="15">
+      <c r="B26" s="13">
         <v>11621182614</v>
       </c>
       <c r="C26" s="7"/>
-      <c r="D26" s="16" t="s">
+      <c r="D26" s="14" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="16" t="s">
+      <c r="E26" s="14" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="14" t="s">
+      <c r="F26" s="12" t="s">
         <v>32</v>
       </c>
       <c r="G26" s="6"/>
-      <c r="H26" s="17">
+      <c r="H26" s="15">
         <v>15</v>
       </c>
-      <c r="I26" s="17">
+      <c r="I26" s="15">
         <v>9</v>
       </c>
-      <c r="J26" s="15">
+      <c r="J26" s="13">
         <v>2016</v>
       </c>
-      <c r="K26" s="11" t="s">
+      <c r="K26" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L26" s="11" t="s">
+      <c r="L26" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M26" s="9"/>
-      <c r="N26" s="11">
+      <c r="M26" s="8"/>
+      <c r="N26" s="9">
         <v>10</v>
       </c>
-      <c r="O26" s="11">
+      <c r="O26" s="9">
         <v>10</v>
       </c>
-      <c r="P26" s="11">
+      <c r="P26" s="9">
         <v>33</v>
       </c>
       <c r="Q26" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="R26" s="17" t="s">
+      <c r="R26" s="15" t="s">
         <v>114</v>
       </c>
-      <c r="S26" s="15">
+      <c r="S26" s="13">
         <v>21182614</v>
       </c>
-      <c r="T26" s="15">
+      <c r="T26" s="13">
         <v>4269008536</v>
       </c>
-      <c r="U26" s="15" t="s">
+      <c r="U26" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="V26" s="19" t="s">
+      <c r="V26" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="27" spans="1:22" ht="16.5">
+    <row r="27" spans="1:26" ht="16.5">
       <c r="A27" s="6">
         <v>17</v>
       </c>
-      <c r="B27" s="15">
+      <c r="B27" s="13">
         <v>11622655266</v>
       </c>
       <c r="C27" s="7"/>
-      <c r="D27" s="16" t="s">
+      <c r="D27" s="14" t="s">
         <v>100</v>
       </c>
-      <c r="E27" s="16" t="s">
+      <c r="E27" s="14" t="s">
         <v>101</v>
       </c>
-      <c r="F27" s="14" t="s">
+      <c r="F27" s="12" t="s">
         <v>32</v>
       </c>
       <c r="G27" s="6"/>
-      <c r="H27" s="17">
+      <c r="H27" s="15">
         <v>23</v>
       </c>
-      <c r="I27" s="17">
+      <c r="I27" s="15">
         <v>8</v>
       </c>
-      <c r="J27" s="15">
+      <c r="J27" s="13">
         <v>2016</v>
       </c>
-      <c r="K27" s="11" t="s">
+      <c r="K27" s="9" t="s">
         <v>43</v>
       </c>
-      <c r="L27" s="11" t="s">
+      <c r="L27" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M27" s="9"/>
-      <c r="N27" s="11">
+      <c r="M27" s="8"/>
+      <c r="N27" s="9">
         <v>12</v>
       </c>
-      <c r="O27" s="11">
+      <c r="O27" s="9">
         <v>12</v>
       </c>
-      <c r="P27" s="11">
+      <c r="P27" s="9">
         <v>34</v>
       </c>
       <c r="Q27" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="R27" s="17" t="s">
+      <c r="R27" s="15" t="s">
         <v>116</v>
       </c>
-      <c r="S27" s="15">
+      <c r="S27" s="13">
         <v>22655266</v>
       </c>
-      <c r="T27" s="15">
+      <c r="T27" s="13">
         <v>4128095352</v>
       </c>
-      <c r="U27" s="15" t="s">
+      <c r="U27" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="V27" s="19" t="s">
+      <c r="V27" s="17" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="28" spans="1:22" ht="16.5">
+    <row r="28" spans="1:26" ht="16.5">
       <c r="A28" s="6">
         <v>18</v>
       </c>
-      <c r="B28" s="26">
+      <c r="B28" s="24">
         <v>11719486229</v>
       </c>
       <c r="C28" s="7"/>
-      <c r="D28" s="27" t="s">
+      <c r="D28" s="25" t="s">
         <v>118</v>
       </c>
-      <c r="E28" s="16" t="s">
+      <c r="E28" s="14" t="s">
         <v>119</v>
       </c>
-      <c r="F28" s="14" t="s">
+      <c r="F28" s="12" t="s">
         <v>32</v>
       </c>
       <c r="G28" s="6"/>
-      <c r="H28" s="17">
+      <c r="H28" s="15">
         <v>13</v>
       </c>
-      <c r="I28" s="17">
+      <c r="I28" s="15">
         <v>2</v>
       </c>
-      <c r="J28" s="15">
+      <c r="J28" s="13">
         <v>2017</v>
       </c>
-      <c r="K28" s="11" t="s">
+      <c r="K28" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="L28" s="11" t="s">
+      <c r="L28" s="9" t="s">
         <v>122</v>
       </c>
-      <c r="M28" s="9"/>
-      <c r="N28" s="11">
+      <c r="M28" s="8"/>
+      <c r="N28" s="9">
         <v>10</v>
       </c>
-      <c r="O28" s="11">
+      <c r="O28" s="9">
         <v>10</v>
       </c>
-      <c r="P28" s="11">
+      <c r="P28" s="9">
         <v>31</v>
       </c>
       <c r="Q28" s="6" t="s">
@@ -2538,108 +2556,35 @@
       <c r="R28" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="S28" s="15">
+      <c r="S28" s="13">
         <v>19486229</v>
       </c>
-      <c r="T28" s="15">
+      <c r="T28" s="13">
         <v>4125496682</v>
       </c>
-      <c r="U28" s="15" t="s">
+      <c r="U28" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="V28" s="19" t="s">
+      <c r="V28" s="17" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="29" spans="1:22" ht="15">
-      <c r="A29" s="6"/>
-      <c r="B29" s="7"/>
-      <c r="C29" s="7"/>
-      <c r="D29" s="8"/>
-      <c r="E29" s="7"/>
-      <c r="F29" s="7"/>
-      <c r="G29" s="6"/>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
-      <c r="J29" s="8"/>
-      <c r="K29" s="9"/>
-      <c r="L29" s="9"/>
-      <c r="M29" s="9"/>
-      <c r="N29" s="9"/>
-      <c r="O29" s="9"/>
-      <c r="P29" s="9"/>
-      <c r="Q29" s="9"/>
-      <c r="R29" s="8"/>
-      <c r="S29" s="8"/>
-      <c r="T29" s="8"/>
-      <c r="U29" s="10"/>
-      <c r="V29" s="12"/>
-    </row>
-    <row r="30" spans="1:22" ht="15">
-      <c r="A30" s="6"/>
-      <c r="B30" s="7"/>
-      <c r="C30" s="7"/>
-      <c r="D30" s="6"/>
-      <c r="E30" s="7"/>
-      <c r="F30" s="7"/>
-      <c r="G30" s="6"/>
-      <c r="H30" s="6"/>
-      <c r="I30" s="6"/>
-      <c r="J30" s="6"/>
-      <c r="K30" s="11"/>
-      <c r="L30" s="11"/>
-      <c r="M30" s="9"/>
-      <c r="N30" s="9"/>
-      <c r="O30" s="9"/>
-      <c r="P30" s="9"/>
-      <c r="Q30" s="9"/>
-      <c r="R30" s="6"/>
-      <c r="S30" s="6"/>
-      <c r="T30" s="6"/>
-      <c r="U30" s="12"/>
-      <c r="V30" s="12"/>
-    </row>
-    <row r="31" spans="1:22">
-      <c r="A31" s="12"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="12"/>
-      <c r="G31" s="12"/>
-      <c r="H31" s="12"/>
-      <c r="I31" s="12"/>
-      <c r="J31" s="12"/>
-      <c r="K31" s="12"/>
-      <c r="L31" s="12"/>
-      <c r="M31" s="12"/>
-      <c r="N31" s="12"/>
-      <c r="O31" s="12"/>
-      <c r="P31" s="12"/>
-      <c r="Q31" s="12"/>
-      <c r="R31" s="12"/>
-      <c r="S31" s="12"/>
-      <c r="T31" s="12"/>
-      <c r="U31" s="12"/>
-      <c r="V31" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="Q9:R10"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:V5"/>
+    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="E6:H6"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="AD6:AE6"/>
     <mergeCell ref="M7:N7"/>
     <mergeCell ref="O7:R7"/>
     <mergeCell ref="AB7:AD7"/>
@@ -2651,20 +2596,21 @@
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="K7:L7"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="AD6:AE6"/>
-    <mergeCell ref="S6:V6"/>
-    <mergeCell ref="A5:V5"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="K9:K10"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="Q9:R10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Matricula_4to_grado.xlsx
+++ b/Matricula_4to_grado.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\Project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{77E73439-EC39-4C93-92DD-5EA656F87561}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F345619D-7415-45E2-99EB-DAF23C9D59BC}" xr6:coauthVersionLast="43" xr6:coauthVersionMax="43" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="21840" windowHeight="13140" tabRatio="278" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -420,7 +420,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -429,71 +429,29 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <b/>
-      <sz val="16"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial Narrow"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
     <font>
       <u/>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="Arial"/>
+      <name val="Arial Narrow"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -671,173 +629,136 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="justify" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="justify" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1166,1425 +1087,2040 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A5:AE28"/>
+  <dimension ref="A1:AE37"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="9" style="2"/>
-    <col min="2" max="3" width="16.7109375" style="2" customWidth="1"/>
-    <col min="4" max="4" width="23.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="25.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="17.140625" style="2" customWidth="1"/>
-    <col min="7" max="10" width="9" style="2"/>
-    <col min="11" max="11" width="10.28515625" style="2" customWidth="1"/>
-    <col min="12" max="14" width="9" style="2"/>
-    <col min="15" max="15" width="11.7109375" style="2" customWidth="1"/>
-    <col min="16" max="16" width="9" style="2"/>
-    <col min="17" max="17" width="17.42578125" style="2" customWidth="1"/>
-    <col min="18" max="18" width="22" style="2" customWidth="1"/>
-    <col min="19" max="19" width="20.85546875" style="2" customWidth="1"/>
-    <col min="20" max="20" width="21.85546875" style="2" customWidth="1"/>
-    <col min="21" max="21" width="33.42578125" style="2" customWidth="1"/>
-    <col min="22" max="22" width="22.7109375" style="2" customWidth="1"/>
-    <col min="23" max="24" width="9" style="2"/>
-    <col min="25" max="25" width="13.42578125" style="2" customWidth="1"/>
-    <col min="26" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="9" style="1"/>
+    <col min="2" max="3" width="16.7109375" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.7109375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="25.85546875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="17.140625" style="1" customWidth="1"/>
+    <col min="7" max="10" width="9" style="1"/>
+    <col min="11" max="11" width="10.28515625" style="1" customWidth="1"/>
+    <col min="12" max="14" width="9" style="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" customWidth="1"/>
+    <col min="16" max="16" width="9" style="1"/>
+    <col min="17" max="17" width="17.42578125" style="1" customWidth="1"/>
+    <col min="18" max="18" width="22" style="1" customWidth="1"/>
+    <col min="19" max="19" width="20.85546875" style="1" customWidth="1"/>
+    <col min="20" max="20" width="21.85546875" style="1" customWidth="1"/>
+    <col min="21" max="21" width="33.42578125" style="1" customWidth="1"/>
+    <col min="22" max="22" width="22.7109375" style="1" customWidth="1"/>
+    <col min="23" max="24" width="9" style="1"/>
+    <col min="25" max="25" width="13.42578125" style="1" customWidth="1"/>
+    <col min="26" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
+    <row r="1" spans="1:31" ht="15.75">
+      <c r="A1" s="13"/>
+      <c r="B1" s="13"/>
+      <c r="C1" s="13"/>
+      <c r="D1" s="13"/>
+      <c r="E1" s="13"/>
+      <c r="F1" s="13"/>
+      <c r="G1" s="13"/>
+      <c r="H1" s="13"/>
+      <c r="I1" s="13"/>
+      <c r="J1" s="13"/>
+      <c r="K1" s="13"/>
+      <c r="L1" s="13"/>
+      <c r="M1" s="13"/>
+      <c r="N1" s="13"/>
+      <c r="O1" s="13"/>
+      <c r="P1" s="13"/>
+      <c r="Q1" s="13"/>
+      <c r="R1" s="13"/>
+      <c r="S1" s="13"/>
+      <c r="T1" s="13"/>
+      <c r="U1" s="13"/>
+      <c r="V1" s="13"/>
+      <c r="W1" s="13"/>
+      <c r="X1" s="13"/>
+      <c r="Y1" s="13"/>
+      <c r="Z1" s="13"/>
+      <c r="AA1" s="13"/>
+      <c r="AB1" s="13"/>
+      <c r="AC1" s="13"/>
+      <c r="AD1" s="13"/>
+      <c r="AE1" s="13"/>
+    </row>
+    <row r="2" spans="1:31" ht="15.75">
+      <c r="A2" s="13"/>
+      <c r="B2" s="13"/>
+      <c r="C2" s="13"/>
+      <c r="D2" s="13"/>
+      <c r="E2" s="13"/>
+      <c r="F2" s="13"/>
+      <c r="G2" s="13"/>
+      <c r="H2" s="13"/>
+      <c r="I2" s="13"/>
+      <c r="J2" s="13"/>
+      <c r="K2" s="13"/>
+      <c r="L2" s="13"/>
+      <c r="M2" s="13"/>
+      <c r="N2" s="13"/>
+      <c r="O2" s="13"/>
+      <c r="P2" s="13"/>
+      <c r="Q2" s="13"/>
+      <c r="R2" s="13"/>
+      <c r="S2" s="13"/>
+      <c r="T2" s="13"/>
+      <c r="U2" s="13"/>
+      <c r="V2" s="13"/>
+      <c r="W2" s="13"/>
+      <c r="X2" s="13"/>
+      <c r="Y2" s="13"/>
+      <c r="Z2" s="13"/>
+      <c r="AA2" s="13"/>
+      <c r="AB2" s="13"/>
+      <c r="AC2" s="13"/>
+      <c r="AD2" s="13"/>
+      <c r="AE2" s="13"/>
+    </row>
+    <row r="3" spans="1:31" ht="15.75">
+      <c r="A3" s="13"/>
+      <c r="B3" s="13"/>
+      <c r="C3" s="13"/>
+      <c r="D3" s="13"/>
+      <c r="E3" s="13"/>
+      <c r="F3" s="13"/>
+      <c r="G3" s="13"/>
+      <c r="H3" s="13"/>
+      <c r="I3" s="13"/>
+      <c r="J3" s="13"/>
+      <c r="K3" s="13"/>
+      <c r="L3" s="13"/>
+      <c r="M3" s="13"/>
+      <c r="N3" s="13"/>
+      <c r="O3" s="13"/>
+      <c r="P3" s="13"/>
+      <c r="Q3" s="13"/>
+      <c r="R3" s="13"/>
+      <c r="S3" s="13"/>
+      <c r="T3" s="13"/>
+      <c r="U3" s="13"/>
+      <c r="V3" s="13"/>
+      <c r="W3" s="13"/>
+      <c r="X3" s="13"/>
+      <c r="Y3" s="13"/>
+      <c r="Z3" s="13"/>
+      <c r="AA3" s="13"/>
+      <c r="AB3" s="13"/>
+      <c r="AC3" s="13"/>
+      <c r="AD3" s="13"/>
+      <c r="AE3" s="13"/>
+    </row>
+    <row r="4" spans="1:31" ht="15.75">
+      <c r="A4" s="13"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
+      <c r="N4" s="13"/>
+      <c r="O4" s="13"/>
+      <c r="P4" s="13"/>
+      <c r="Q4" s="13"/>
+      <c r="R4" s="13"/>
+      <c r="S4" s="13"/>
+      <c r="T4" s="13"/>
+      <c r="U4" s="13"/>
+      <c r="V4" s="13"/>
+      <c r="W4" s="13"/>
+      <c r="X4" s="13"/>
+      <c r="Y4" s="13"/>
+      <c r="Z4" s="13"/>
+      <c r="AA4" s="13"/>
+      <c r="AB4" s="13"/>
+      <c r="AC4" s="13"/>
+      <c r="AD4" s="13"/>
+      <c r="AE4" s="13"/>
+    </row>
     <row r="5" spans="1:31" ht="30.95" customHeight="1">
-      <c r="A5" s="57" t="s">
+      <c r="A5" s="14" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="58"/>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
-      <c r="J5" s="58"/>
-      <c r="K5" s="58"/>
-      <c r="L5" s="58"/>
-      <c r="M5" s="58"/>
-      <c r="N5" s="58"/>
-      <c r="O5" s="58"/>
-      <c r="P5" s="58"/>
-      <c r="Q5" s="58"/>
-      <c r="R5" s="58"/>
-      <c r="S5" s="58"/>
-      <c r="T5" s="58"/>
-      <c r="U5" s="58"/>
-      <c r="V5" s="58"/>
-      <c r="W5" s="32"/>
-      <c r="X5" s="32"/>
-      <c r="Y5" s="1"/>
-      <c r="Z5" s="32"/>
-      <c r="AA5" s="32"/>
-      <c r="AB5" s="32"/>
-      <c r="AC5" s="1"/>
-      <c r="AD5" s="32"/>
-      <c r="AE5" s="32"/>
+      <c r="B5" s="15"/>
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="15"/>
+      <c r="H5" s="15"/>
+      <c r="I5" s="15"/>
+      <c r="J5" s="15"/>
+      <c r="K5" s="15"/>
+      <c r="L5" s="15"/>
+      <c r="M5" s="15"/>
+      <c r="N5" s="15"/>
+      <c r="O5" s="15"/>
+      <c r="P5" s="15"/>
+      <c r="Q5" s="15"/>
+      <c r="R5" s="15"/>
+      <c r="S5" s="15"/>
+      <c r="T5" s="15"/>
+      <c r="U5" s="15"/>
+      <c r="V5" s="15"/>
+      <c r="W5" s="16"/>
+      <c r="X5" s="16"/>
+      <c r="Y5" s="17"/>
+      <c r="Z5" s="16"/>
+      <c r="AA5" s="16"/>
+      <c r="AB5" s="16"/>
+      <c r="AC5" s="17"/>
+      <c r="AD5" s="16"/>
+      <c r="AE5" s="16"/>
     </row>
     <row r="6" spans="1:31" ht="27.95" customHeight="1">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="18" t="s">
         <v>123</v>
       </c>
-      <c r="B6" s="55"/>
-      <c r="C6" s="54" t="s">
+      <c r="B6" s="19"/>
+      <c r="C6" s="18" t="s">
         <v>121</v>
       </c>
-      <c r="D6" s="55"/>
-      <c r="E6" s="54" t="s">
+      <c r="D6" s="19"/>
+      <c r="E6" s="18" t="s">
         <v>126</v>
       </c>
-      <c r="F6" s="56"/>
-      <c r="G6" s="56"/>
-      <c r="H6" s="55"/>
-      <c r="I6" s="54" t="s">
+      <c r="F6" s="20"/>
+      <c r="G6" s="20"/>
+      <c r="H6" s="19"/>
+      <c r="I6" s="18" t="s">
         <v>124</v>
       </c>
-      <c r="J6" s="56"/>
-      <c r="K6" s="56"/>
-      <c r="L6" s="55"/>
-      <c r="M6" s="54" t="s">
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="19"/>
+      <c r="M6" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="N6" s="56"/>
-      <c r="O6" s="56"/>
-      <c r="P6" s="55"/>
-      <c r="Q6" s="54" t="s">
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="19"/>
+      <c r="Q6" s="18" t="s">
         <v>36</v>
       </c>
-      <c r="R6" s="55"/>
-      <c r="S6" s="36" t="s">
+      <c r="R6" s="19"/>
+      <c r="S6" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="T6" s="37"/>
-      <c r="U6" s="37"/>
-      <c r="V6" s="38"/>
-      <c r="W6" s="32"/>
-      <c r="X6" s="32"/>
-      <c r="Z6" s="35"/>
-      <c r="AA6" s="35"/>
-      <c r="AB6" s="35"/>
-      <c r="AC6" s="1"/>
-      <c r="AD6" s="35"/>
-      <c r="AE6" s="35"/>
+      <c r="T6" s="22"/>
+      <c r="U6" s="22"/>
+      <c r="V6" s="23"/>
+      <c r="W6" s="16"/>
+      <c r="X6" s="16"/>
+      <c r="Y6" s="13"/>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="17"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
     </row>
     <row r="7" spans="1:31" ht="36" customHeight="1">
-      <c r="A7" s="54" t="s">
+      <c r="A7" s="18" t="s">
         <v>125</v>
       </c>
-      <c r="B7" s="56"/>
-      <c r="C7" s="55"/>
-      <c r="D7" s="51" t="s">
+      <c r="B7" s="20"/>
+      <c r="C7" s="19"/>
+      <c r="D7" s="25" t="s">
         <v>0</v>
       </c>
-      <c r="E7" s="53"/>
-      <c r="F7" s="51" t="s">
+      <c r="E7" s="26"/>
+      <c r="F7" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="G7" s="53"/>
-      <c r="H7" s="51" t="s">
+      <c r="G7" s="26"/>
+      <c r="H7" s="25" t="s">
         <v>2</v>
       </c>
-      <c r="I7" s="52"/>
-      <c r="J7" s="53"/>
-      <c r="K7" s="54" t="s">
+      <c r="I7" s="27"/>
+      <c r="J7" s="26"/>
+      <c r="K7" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="L7" s="55"/>
-      <c r="M7" s="51" t="s">
+      <c r="L7" s="19"/>
+      <c r="M7" s="25" t="s">
         <v>38</v>
       </c>
-      <c r="N7" s="53"/>
-      <c r="O7" s="51" t="s">
+      <c r="N7" s="26"/>
+      <c r="O7" s="25" t="s">
         <v>39</v>
       </c>
-      <c r="P7" s="52"/>
-      <c r="Q7" s="52"/>
-      <c r="R7" s="53"/>
-      <c r="S7" s="11" t="s">
+      <c r="P7" s="27"/>
+      <c r="Q7" s="27"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="T7" s="11" t="s">
+      <c r="T7" s="28" t="s">
         <v>40</v>
       </c>
-      <c r="U7" s="33" t="s">
+      <c r="U7" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="V7" s="34"/>
-      <c r="W7" s="3"/>
-      <c r="AA7" s="1" t="s">
+      <c r="V7" s="23"/>
+      <c r="W7" s="29"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="13"/>
+      <c r="Z7" s="13"/>
+      <c r="AA7" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="AB7" s="32"/>
-      <c r="AC7" s="32"/>
-      <c r="AD7" s="32"/>
-      <c r="AE7" s="4"/>
+      <c r="AB7" s="16"/>
+      <c r="AC7" s="16"/>
+      <c r="AD7" s="16"/>
+      <c r="AE7" s="30"/>
     </row>
     <row r="8" spans="1:31" ht="17.100000000000001" customHeight="1">
-      <c r="A8" s="48" t="s">
+      <c r="A8" s="31" t="s">
         <v>4</v>
       </c>
-      <c r="B8" s="49"/>
-      <c r="C8" s="49"/>
-      <c r="D8" s="49"/>
-      <c r="E8" s="49"/>
-      <c r="F8" s="49"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="49"/>
-      <c r="I8" s="49"/>
-      <c r="J8" s="49"/>
-      <c r="K8" s="49"/>
-      <c r="L8" s="49"/>
-      <c r="M8" s="49"/>
-      <c r="N8" s="49"/>
-      <c r="O8" s="49"/>
-      <c r="P8" s="50"/>
-      <c r="Q8" s="48" t="s">
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="32"/>
+      <c r="F8" s="32"/>
+      <c r="G8" s="32"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="33"/>
+      <c r="Q8" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="R8" s="49"/>
-      <c r="S8" s="49"/>
-      <c r="T8" s="49"/>
-      <c r="U8" s="49"/>
-      <c r="V8" s="49"/>
-      <c r="W8" s="4"/>
-      <c r="X8" s="1"/>
-      <c r="Y8" s="1"/>
-      <c r="Z8" s="1"/>
-      <c r="AA8" s="1"/>
-      <c r="AB8" s="1"/>
-      <c r="AC8" s="1"/>
-      <c r="AD8" s="1"/>
-      <c r="AE8" s="4"/>
-    </row>
-    <row r="9" spans="1:31" ht="15">
-      <c r="A9" s="30" t="s">
+      <c r="R8" s="32"/>
+      <c r="S8" s="32"/>
+      <c r="T8" s="32"/>
+      <c r="U8" s="32"/>
+      <c r="V8" s="32"/>
+      <c r="W8" s="30"/>
+      <c r="X8" s="17"/>
+      <c r="Y8" s="17"/>
+      <c r="Z8" s="17"/>
+      <c r="AA8" s="17"/>
+      <c r="AB8" s="17"/>
+      <c r="AC8" s="17"/>
+      <c r="AD8" s="17"/>
+      <c r="AE8" s="30"/>
+    </row>
+    <row r="9" spans="1:31" ht="15.75">
+      <c r="A9" s="34" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="30" t="s">
+      <c r="B9" s="34" t="s">
         <v>7</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="D9" s="44" t="s">
+      <c r="D9" s="35" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="45"/>
-      <c r="F9" s="30" t="s">
+      <c r="E9" s="36"/>
+      <c r="F9" s="34" t="s">
         <v>23</v>
       </c>
-      <c r="G9" s="30" t="s">
+      <c r="G9" s="34" t="s">
         <v>10</v>
       </c>
-      <c r="H9" s="41" t="s">
+      <c r="H9" s="37" t="s">
         <v>11</v>
       </c>
-      <c r="I9" s="42"/>
-      <c r="J9" s="43"/>
-      <c r="K9" s="30" t="s">
+      <c r="I9" s="38"/>
+      <c r="J9" s="39"/>
+      <c r="K9" s="34" t="s">
         <v>12</v>
       </c>
-      <c r="L9" s="41" t="s">
+      <c r="L9" s="37" t="s">
         <v>13</v>
       </c>
-      <c r="M9" s="43"/>
-      <c r="N9" s="41" t="s">
+      <c r="M9" s="39"/>
+      <c r="N9" s="37" t="s">
         <v>24</v>
       </c>
-      <c r="O9" s="42"/>
-      <c r="P9" s="43"/>
-      <c r="Q9" s="26" t="s">
+      <c r="O9" s="38"/>
+      <c r="P9" s="39"/>
+      <c r="Q9" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="R9" s="27"/>
-      <c r="S9" s="30" t="s">
+      <c r="R9" s="36"/>
+      <c r="S9" s="34" t="s">
         <v>8</v>
       </c>
-      <c r="T9" s="30" t="s">
+      <c r="T9" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="U9" s="30" t="s">
+      <c r="U9" s="34" t="s">
         <v>26</v>
       </c>
-      <c r="V9" s="39" t="s">
+      <c r="V9" s="40" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="10" spans="1:31" ht="15">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="31"/>
-      <c r="D10" s="46"/>
-      <c r="E10" s="47"/>
-      <c r="F10" s="31"/>
-      <c r="G10" s="31"/>
-      <c r="H10" s="5" t="s">
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="13"/>
+      <c r="Z9" s="13"/>
+      <c r="AA9" s="13"/>
+      <c r="AB9" s="13"/>
+      <c r="AC9" s="13"/>
+      <c r="AD9" s="13"/>
+      <c r="AE9" s="13"/>
+    </row>
+    <row r="10" spans="1:31" ht="15.75">
+      <c r="A10" s="41"/>
+      <c r="B10" s="41"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="42"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="41"/>
+      <c r="G10" s="41"/>
+      <c r="H10" s="44" t="s">
         <v>15</v>
       </c>
-      <c r="I10" s="5" t="s">
+      <c r="I10" s="44" t="s">
         <v>16</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="44" t="s">
         <v>17</v>
       </c>
-      <c r="K10" s="31"/>
-      <c r="L10" s="5" t="s">
+      <c r="K10" s="41"/>
+      <c r="L10" s="44" t="s">
         <v>18</v>
       </c>
-      <c r="M10" s="5" t="s">
+      <c r="M10" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="N10" s="5" t="s">
+      <c r="N10" s="44" t="s">
         <v>20</v>
       </c>
-      <c r="O10" s="5" t="s">
+      <c r="O10" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="P10" s="5" t="s">
+      <c r="P10" s="44" t="s">
         <v>22</v>
       </c>
-      <c r="Q10" s="28"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="31"/>
-      <c r="T10" s="31"/>
-      <c r="U10" s="31"/>
-      <c r="V10" s="40"/>
-    </row>
-    <row r="11" spans="1:31" ht="16.5">
-      <c r="A11" s="6">
+      <c r="Q10" s="42"/>
+      <c r="R10" s="43"/>
+      <c r="S10" s="41"/>
+      <c r="T10" s="41"/>
+      <c r="U10" s="41"/>
+      <c r="V10" s="45"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="13"/>
+      <c r="Z10" s="13"/>
+      <c r="AA10" s="13"/>
+      <c r="AB10" s="13"/>
+      <c r="AC10" s="13"/>
+      <c r="AD10" s="13"/>
+      <c r="AE10" s="13"/>
+    </row>
+    <row r="11" spans="1:31" ht="15.75">
+      <c r="A11" s="4">
         <v>1</v>
       </c>
-      <c r="B11" s="10"/>
-      <c r="C11" s="13">
+      <c r="B11" s="3"/>
+      <c r="C11" s="2">
         <v>36825110</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="F11" s="13" t="s">
+      <c r="F11" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G11" s="6"/>
-      <c r="H11" s="18">
+      <c r="G11" s="4"/>
+      <c r="H11" s="4">
         <v>8</v>
       </c>
-      <c r="I11" s="18">
+      <c r="I11" s="4">
         <v>2</v>
       </c>
-      <c r="J11" s="19">
+      <c r="J11" s="5">
         <v>2015</v>
       </c>
-      <c r="K11" s="9" t="s">
+      <c r="K11" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L11" s="9" t="s">
+      <c r="L11" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M11" s="8"/>
-      <c r="N11" s="9">
+      <c r="M11" s="5"/>
+      <c r="N11" s="5">
         <v>10</v>
       </c>
-      <c r="O11" s="9">
+      <c r="O11" s="5">
         <v>10</v>
       </c>
-      <c r="P11" s="9">
+      <c r="P11" s="5">
         <v>36</v>
       </c>
-      <c r="Q11" s="6" t="s">
+      <c r="Q11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="R11" s="6" t="s">
+      <c r="R11" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="S11" s="13">
+      <c r="S11" s="2">
         <v>25560232</v>
       </c>
-      <c r="T11" s="13">
+      <c r="T11" s="2">
         <v>4129743760</v>
       </c>
-      <c r="U11" s="13" t="s">
+      <c r="U11" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V11" s="17" t="s">
+      <c r="V11" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="12" spans="1:31" ht="16.5">
-      <c r="A12" s="6">
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="13"/>
+    </row>
+    <row r="12" spans="1:31" ht="15.75">
+      <c r="A12" s="4">
         <v>2</v>
       </c>
-      <c r="C12" s="13">
+      <c r="B12" s="13"/>
+      <c r="C12" s="2">
         <v>36946904</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="F12" s="13" t="s">
+      <c r="F12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G12" s="6"/>
-      <c r="H12" s="18">
+      <c r="G12" s="4"/>
+      <c r="H12" s="4">
         <v>6</v>
       </c>
-      <c r="I12" s="18">
+      <c r="I12" s="4">
         <v>2</v>
       </c>
-      <c r="J12" s="19">
+      <c r="J12" s="5">
         <v>2016</v>
       </c>
-      <c r="K12" s="9" t="s">
+      <c r="K12" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L12" s="9" t="s">
+      <c r="L12" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M12" s="8"/>
-      <c r="N12" s="9">
+      <c r="M12" s="5"/>
+      <c r="N12" s="5">
         <v>12</v>
       </c>
-      <c r="O12" s="9">
+      <c r="O12" s="5">
         <v>12</v>
       </c>
-      <c r="P12" s="9">
+      <c r="P12" s="5">
         <v>35</v>
       </c>
-      <c r="Q12" s="6" t="s">
+      <c r="Q12" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="R12" s="6" t="s">
+      <c r="R12" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="S12" s="13">
+      <c r="S12" s="2">
         <v>19894172</v>
       </c>
-      <c r="T12" s="13">
+      <c r="T12" s="2">
         <v>4127932191</v>
       </c>
-      <c r="U12" s="13" t="s">
+      <c r="U12" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="V12" s="17" t="s">
+      <c r="V12" s="2" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="13" spans="1:31" ht="16.5">
-      <c r="A13" s="6">
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="13"/>
+      <c r="Z12" s="13"/>
+      <c r="AA12" s="13"/>
+      <c r="AB12" s="13"/>
+      <c r="AC12" s="13"/>
+      <c r="AD12" s="13"/>
+      <c r="AE12" s="13"/>
+    </row>
+    <row r="13" spans="1:31" ht="15.75">
+      <c r="A13" s="4">
         <v>3</v>
       </c>
-      <c r="B13" s="7"/>
-      <c r="C13" s="13">
+      <c r="B13" s="4"/>
+      <c r="C13" s="2">
         <v>37120471</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="F13" s="13" t="s">
+      <c r="F13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G13" s="6"/>
-      <c r="H13" s="15">
+      <c r="G13" s="4"/>
+      <c r="H13" s="6">
         <v>1</v>
       </c>
-      <c r="I13" s="15">
+      <c r="I13" s="6">
         <v>9</v>
       </c>
-      <c r="J13" s="13">
+      <c r="J13" s="2">
         <v>2014</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="K13" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="L13" s="12" t="s">
+      <c r="L13" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="M13" s="8"/>
-      <c r="N13" s="9">
+      <c r="M13" s="5"/>
+      <c r="N13" s="5">
         <v>14</v>
       </c>
-      <c r="O13" s="9">
+      <c r="O13" s="5">
         <v>14</v>
       </c>
-      <c r="P13" s="9">
+      <c r="P13" s="5">
         <v>37</v>
       </c>
-      <c r="Q13" s="6" t="s">
+      <c r="Q13" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="R13" s="6" t="s">
+      <c r="R13" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="S13" s="13">
+      <c r="S13" s="2">
         <v>22655608</v>
       </c>
-      <c r="T13" s="13">
+      <c r="T13" s="2">
         <v>4121338291</v>
       </c>
-      <c r="U13" s="13" t="s">
+      <c r="U13" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V13" s="17" t="s">
+      <c r="V13" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="14" spans="1:31" ht="16.5">
-      <c r="A14" s="6">
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="13"/>
+      <c r="Z13" s="13"/>
+      <c r="AA13" s="13"/>
+      <c r="AB13" s="13"/>
+      <c r="AC13" s="13"/>
+      <c r="AD13" s="13"/>
+      <c r="AE13" s="13"/>
+    </row>
+    <row r="14" spans="1:31" ht="15.75">
+      <c r="A14" s="4">
         <v>4</v>
       </c>
-      <c r="B14" s="7"/>
-      <c r="C14" s="13">
+      <c r="B14" s="4"/>
+      <c r="C14" s="2">
         <v>37302811</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="F14" s="13" t="s">
+      <c r="F14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G14" s="6"/>
-      <c r="H14" s="15">
+      <c r="G14" s="4"/>
+      <c r="H14" s="6">
         <v>9</v>
       </c>
-      <c r="I14" s="15">
+      <c r="I14" s="6">
         <v>10</v>
       </c>
-      <c r="J14" s="13">
+      <c r="J14" s="2">
         <v>2015</v>
       </c>
-      <c r="K14" s="9" t="s">
+      <c r="K14" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L14" s="9"/>
-      <c r="M14" s="9" t="s">
+      <c r="L14" s="5"/>
+      <c r="M14" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="N14" s="9">
+      <c r="N14" s="5">
         <v>12</v>
       </c>
-      <c r="O14" s="9">
+      <c r="O14" s="5">
         <v>12</v>
       </c>
-      <c r="P14" s="9">
+      <c r="P14" s="5">
         <v>35</v>
       </c>
-      <c r="Q14" s="6" t="s">
+      <c r="Q14" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="R14" s="6" t="s">
+      <c r="R14" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="S14" s="13">
+      <c r="S14" s="2">
         <v>19247972</v>
       </c>
-      <c r="T14" s="13">
+      <c r="T14" s="2">
         <v>4262178897</v>
       </c>
-      <c r="U14" s="13" t="s">
+      <c r="U14" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="V14" s="17" t="s">
+      <c r="V14" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="15" spans="1:31" ht="16.5">
-      <c r="A15" s="6">
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="13"/>
+      <c r="Z14" s="13"/>
+      <c r="AA14" s="13"/>
+      <c r="AB14" s="13"/>
+      <c r="AC14" s="13"/>
+      <c r="AD14" s="13"/>
+      <c r="AE14" s="13"/>
+    </row>
+    <row r="15" spans="1:31" ht="15.75">
+      <c r="A15" s="4">
         <v>5</v>
       </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="13">
+      <c r="B15" s="4"/>
+      <c r="C15" s="2">
         <v>37302842</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G15" s="6"/>
-      <c r="H15" s="15">
+      <c r="G15" s="4"/>
+      <c r="H15" s="6">
         <v>15</v>
       </c>
-      <c r="I15" s="15">
+      <c r="I15" s="6">
         <v>6</v>
       </c>
-      <c r="J15" s="13">
+      <c r="J15" s="2">
         <v>2016</v>
       </c>
-      <c r="K15" s="9" t="s">
+      <c r="K15" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L15" s="9" t="s">
+      <c r="L15" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M15" s="8"/>
-      <c r="N15" s="9">
+      <c r="M15" s="5"/>
+      <c r="N15" s="5">
         <v>12</v>
       </c>
-      <c r="O15" s="9">
+      <c r="O15" s="5">
         <v>12</v>
       </c>
-      <c r="P15" s="9">
+      <c r="P15" s="5">
         <v>34</v>
       </c>
-      <c r="Q15" s="6" t="s">
+      <c r="Q15" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="R15" s="6" t="s">
+      <c r="R15" s="4" t="s">
         <v>68</v>
       </c>
-      <c r="S15" s="13">
+      <c r="S15" s="2">
         <v>17521672</v>
       </c>
-      <c r="T15" s="13">
+      <c r="T15" s="2">
         <v>4122783453</v>
       </c>
-      <c r="U15" s="13" t="s">
+      <c r="U15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="V15" s="17" t="s">
+      <c r="V15" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" spans="1:31" ht="16.5">
-      <c r="A16" s="6">
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="13"/>
+      <c r="Z15" s="13"/>
+      <c r="AA15" s="13"/>
+      <c r="AB15" s="13"/>
+      <c r="AC15" s="13"/>
+      <c r="AD15" s="13"/>
+      <c r="AE15" s="13"/>
+    </row>
+    <row r="16" spans="1:31" ht="15.75">
+      <c r="A16" s="4">
         <v>6</v>
       </c>
-      <c r="B16" s="7"/>
-      <c r="C16" s="13">
+      <c r="B16" s="4"/>
+      <c r="C16" s="2">
         <v>37375148</v>
       </c>
-      <c r="D16" s="16" t="s">
+      <c r="D16" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="E16" s="16" t="s">
+      <c r="E16" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="F16" s="13" t="s">
+      <c r="F16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G16" s="6"/>
-      <c r="H16" s="15">
+      <c r="G16" s="4"/>
+      <c r="H16" s="6">
         <v>25</v>
       </c>
-      <c r="I16" s="15">
+      <c r="I16" s="6">
         <v>7</v>
       </c>
-      <c r="J16" s="13">
+      <c r="J16" s="2">
         <v>2016</v>
       </c>
-      <c r="K16" s="9" t="s">
+      <c r="K16" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L16" s="9" t="s">
+      <c r="L16" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M16" s="8"/>
-      <c r="N16" s="9">
+      <c r="M16" s="5"/>
+      <c r="N16" s="5">
         <v>10</v>
       </c>
-      <c r="O16" s="9">
+      <c r="O16" s="5">
         <v>10</v>
       </c>
-      <c r="P16" s="9">
+      <c r="P16" s="5">
         <v>35</v>
       </c>
-      <c r="Q16" s="6" t="s">
+      <c r="Q16" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="R16" s="6" t="s">
+      <c r="R16" s="4" t="s">
         <v>70</v>
       </c>
-      <c r="S16" s="13">
+      <c r="S16" s="2">
         <v>15756707</v>
       </c>
-      <c r="T16" s="13">
+      <c r="T16" s="2">
         <v>4262783746</v>
       </c>
-      <c r="U16" s="13" t="s">
+      <c r="U16" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="V16" s="17" t="s">
+      <c r="V16" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="17" spans="1:26" ht="16.5">
-      <c r="A17" s="6">
+      <c r="W16" s="13"/>
+      <c r="X16" s="13"/>
+      <c r="Y16" s="13"/>
+      <c r="Z16" s="13"/>
+      <c r="AA16" s="13"/>
+      <c r="AB16" s="13"/>
+      <c r="AC16" s="13"/>
+      <c r="AD16" s="13"/>
+      <c r="AE16" s="13"/>
+    </row>
+    <row r="17" spans="1:31" ht="15.75">
+      <c r="A17" s="4">
         <v>7</v>
       </c>
-      <c r="B17" s="13">
+      <c r="B17" s="2">
         <v>11611954667</v>
       </c>
-      <c r="C17" s="10"/>
-      <c r="D17" s="16" t="s">
+      <c r="C17" s="3"/>
+      <c r="D17" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="E17" s="16" t="s">
+      <c r="E17" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="F17" s="13" t="s">
+      <c r="F17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G17" s="6"/>
-      <c r="H17" s="15">
+      <c r="G17" s="4"/>
+      <c r="H17" s="6">
         <v>29</v>
       </c>
-      <c r="I17" s="15">
+      <c r="I17" s="6">
         <v>11</v>
       </c>
-      <c r="J17" s="13">
+      <c r="J17" s="2">
         <v>2016</v>
       </c>
-      <c r="K17" s="9" t="s">
+      <c r="K17" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L17" s="9" t="s">
+      <c r="L17" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M17" s="8"/>
-      <c r="N17" s="9">
+      <c r="M17" s="5"/>
+      <c r="N17" s="5">
         <v>12</v>
       </c>
-      <c r="O17" s="9">
+      <c r="O17" s="5">
         <v>12</v>
       </c>
-      <c r="P17" s="9">
+      <c r="P17" s="5">
         <v>34</v>
       </c>
-      <c r="Q17" s="6" t="s">
+      <c r="Q17" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="R17" s="6" t="s">
+      <c r="R17" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="S17" s="13">
+      <c r="S17" s="2">
         <v>11954667</v>
       </c>
-      <c r="T17" s="13">
+      <c r="T17" s="2">
         <v>4127852674</v>
       </c>
-      <c r="U17" s="13" t="s">
+      <c r="U17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="V17" s="17" t="s">
+      <c r="V17" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="18" spans="1:26" ht="16.5">
-      <c r="A18" s="6">
+      <c r="W17" s="13"/>
+      <c r="X17" s="13"/>
+      <c r="Y17" s="13"/>
+      <c r="Z17" s="13"/>
+      <c r="AA17" s="13"/>
+      <c r="AB17" s="13"/>
+      <c r="AC17" s="13"/>
+      <c r="AD17" s="13"/>
+      <c r="AE17" s="13"/>
+    </row>
+    <row r="18" spans="1:31" ht="15.75">
+      <c r="A18" s="4">
         <v>8</v>
       </c>
-      <c r="B18" s="13">
+      <c r="B18" s="2">
         <v>11614588352</v>
       </c>
-      <c r="C18" s="10"/>
-      <c r="D18" s="16" t="s">
+      <c r="C18" s="3"/>
+      <c r="D18" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="E18" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="F18" s="13" t="s">
+      <c r="F18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G18" s="6"/>
-      <c r="H18" s="15">
+      <c r="G18" s="4"/>
+      <c r="H18" s="6">
         <v>31</v>
       </c>
-      <c r="I18" s="15">
+      <c r="I18" s="6">
         <v>12</v>
       </c>
-      <c r="J18" s="13">
+      <c r="J18" s="2">
         <v>2016</v>
       </c>
-      <c r="K18" s="9" t="s">
+      <c r="K18" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L18" s="9" t="s">
+      <c r="L18" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M18" s="8"/>
-      <c r="N18" s="9">
+      <c r="M18" s="5"/>
+      <c r="N18" s="5">
         <v>10</v>
       </c>
-      <c r="O18" s="9">
+      <c r="O18" s="5">
         <v>10</v>
       </c>
-      <c r="P18" s="9">
+      <c r="P18" s="5">
         <v>33</v>
       </c>
-      <c r="Q18" s="6" t="s">
+      <c r="Q18" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="R18" s="6" t="s">
+      <c r="R18" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="S18" s="13">
+      <c r="S18" s="2">
         <v>17522003</v>
       </c>
-      <c r="T18" s="13">
+      <c r="T18" s="2">
         <v>4122391903</v>
       </c>
-      <c r="U18" s="13" t="s">
+      <c r="U18" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="V18" s="17" t="s">
+      <c r="V18" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" ht="16.5">
-      <c r="A19" s="6">
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="13"/>
+      <c r="Z18" s="13"/>
+      <c r="AA18" s="13"/>
+      <c r="AB18" s="13"/>
+      <c r="AC18" s="13"/>
+      <c r="AD18" s="13"/>
+      <c r="AE18" s="13"/>
+    </row>
+    <row r="19" spans="1:31" ht="15.75">
+      <c r="A19" s="4">
         <v>9</v>
       </c>
-      <c r="B19" s="13">
+      <c r="B19" s="2">
         <v>11616664117</v>
       </c>
-      <c r="C19" s="10"/>
-      <c r="D19" s="16" t="s">
+      <c r="C19" s="3"/>
+      <c r="D19" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="E19" s="16" t="s">
+      <c r="E19" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="F19" s="13" t="s">
+      <c r="F19" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G19" s="6"/>
-      <c r="H19" s="15">
+      <c r="G19" s="4"/>
+      <c r="H19" s="6">
         <v>23</v>
       </c>
-      <c r="I19" s="15">
+      <c r="I19" s="6">
         <v>9</v>
       </c>
-      <c r="J19" s="13">
+      <c r="J19" s="2">
         <v>2016</v>
       </c>
-      <c r="K19" s="9" t="s">
+      <c r="K19" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L19" s="9" t="s">
+      <c r="L19" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M19" s="8"/>
-      <c r="N19" s="9">
+      <c r="M19" s="5"/>
+      <c r="N19" s="5">
         <v>10</v>
       </c>
-      <c r="O19" s="9">
+      <c r="O19" s="5">
         <v>8</v>
       </c>
-      <c r="P19" s="9">
+      <c r="P19" s="5">
         <v>35</v>
       </c>
-      <c r="Q19" s="6" t="s">
+      <c r="Q19" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="R19" s="6" t="s">
+      <c r="R19" s="4" t="s">
         <v>82</v>
       </c>
-      <c r="S19" s="13">
+      <c r="S19" s="2">
         <v>16664117</v>
       </c>
-      <c r="T19" s="13">
+      <c r="T19" s="2">
         <v>4268144007</v>
       </c>
-      <c r="U19" s="13" t="s">
+      <c r="U19" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V19" s="17" t="s">
+      <c r="V19" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="Z19" s="59"/>
-    </row>
-    <row r="20" spans="1:26" ht="16.5">
-      <c r="A20" s="6">
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="13"/>
+      <c r="Z19" s="46"/>
+      <c r="AA19" s="13"/>
+      <c r="AB19" s="13"/>
+      <c r="AC19" s="13"/>
+      <c r="AD19" s="13"/>
+      <c r="AE19" s="13"/>
+    </row>
+    <row r="20" spans="1:31" ht="15.75">
+      <c r="A20" s="4">
         <v>10</v>
       </c>
-      <c r="B20" s="13">
+      <c r="B20" s="2">
         <v>11618965516</v>
       </c>
-      <c r="D20" s="14" t="s">
+      <c r="C20" s="13"/>
+      <c r="D20" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="E20" s="14" t="s">
+      <c r="E20" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F20" s="12" t="s">
+      <c r="F20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G20" s="6"/>
-      <c r="H20" s="15">
+      <c r="G20" s="4"/>
+      <c r="H20" s="6">
         <v>13</v>
       </c>
-      <c r="I20" s="15">
+      <c r="I20" s="6">
         <v>2</v>
       </c>
-      <c r="J20" s="13">
+      <c r="J20" s="2">
         <v>2017</v>
       </c>
-      <c r="K20" s="9" t="s">
+      <c r="K20" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L20" s="9" t="s">
+      <c r="L20" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M20" s="8"/>
-      <c r="N20" s="9">
+      <c r="M20" s="5"/>
+      <c r="N20" s="5">
         <v>10</v>
       </c>
-      <c r="O20" s="9">
+      <c r="O20" s="5">
         <v>10</v>
       </c>
-      <c r="P20" s="9">
+      <c r="P20" s="5">
         <v>33</v>
       </c>
-      <c r="Q20" s="6" t="s">
+      <c r="Q20" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="R20" s="6" t="s">
+      <c r="R20" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="S20" s="13">
+      <c r="S20" s="2">
         <v>18965516</v>
       </c>
-      <c r="T20" s="13">
+      <c r="T20" s="2">
         <v>4126878376</v>
       </c>
-      <c r="U20" s="12" t="s">
+      <c r="U20" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="V20" s="17" t="s">
+      <c r="V20" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" ht="16.5">
-      <c r="A21" s="6">
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="13"/>
+      <c r="Z20" s="13"/>
+      <c r="AA20" s="13"/>
+      <c r="AB20" s="13"/>
+      <c r="AC20" s="13"/>
+      <c r="AD20" s="13"/>
+      <c r="AE20" s="13"/>
+    </row>
+    <row r="21" spans="1:31" ht="15.75">
+      <c r="A21" s="4">
         <v>11</v>
       </c>
-      <c r="B21" s="13">
+      <c r="B21" s="2">
         <v>11619486274</v>
       </c>
-      <c r="C21" s="7"/>
-      <c r="D21" s="14" t="s">
+      <c r="C21" s="4"/>
+      <c r="D21" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="E21" s="14" t="s">
+      <c r="E21" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="F21" s="12" t="s">
+      <c r="F21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G21" s="6"/>
-      <c r="H21" s="15">
+      <c r="G21" s="4"/>
+      <c r="H21" s="6">
         <v>13</v>
       </c>
-      <c r="I21" s="15">
+      <c r="I21" s="6">
         <v>12</v>
       </c>
-      <c r="J21" s="13">
+      <c r="J21" s="2">
         <v>2016</v>
       </c>
-      <c r="K21" s="9" t="s">
+      <c r="K21" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L21" s="9" t="s">
+      <c r="L21" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M21" s="8"/>
-      <c r="N21" s="9">
+      <c r="M21" s="5"/>
+      <c r="N21" s="5">
         <v>10</v>
       </c>
-      <c r="O21" s="9">
+      <c r="O21" s="5">
         <v>10</v>
       </c>
-      <c r="P21" s="9">
+      <c r="P21" s="5">
         <v>33</v>
       </c>
-      <c r="Q21" s="6" t="s">
+      <c r="Q21" s="4" t="s">
         <v>52</v>
       </c>
-      <c r="R21" s="15" t="s">
+      <c r="R21" s="6" t="s">
         <v>105</v>
       </c>
-      <c r="S21" s="13">
+      <c r="S21" s="2">
         <v>19486274</v>
       </c>
-      <c r="T21" s="23">
+      <c r="T21" s="7">
         <v>4262370806</v>
       </c>
-      <c r="U21" s="13" t="s">
+      <c r="U21" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V21" s="17" t="s">
+      <c r="V21" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" ht="16.5">
-      <c r="A22" s="6">
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="13"/>
+      <c r="Z21" s="13"/>
+      <c r="AA21" s="13"/>
+      <c r="AB21" s="13"/>
+      <c r="AC21" s="13"/>
+      <c r="AD21" s="13"/>
+      <c r="AE21" s="13"/>
+    </row>
+    <row r="22" spans="1:31" ht="15.75">
+      <c r="A22" s="4">
         <v>12</v>
       </c>
-      <c r="B22" s="13">
+      <c r="B22" s="2">
         <v>11619486376</v>
       </c>
-      <c r="C22" s="7"/>
-      <c r="D22" s="14" t="s">
+      <c r="C22" s="4"/>
+      <c r="D22" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="E22" s="14" t="s">
+      <c r="E22" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="F22" s="12" t="s">
+      <c r="F22" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G22" s="6"/>
-      <c r="H22" s="15">
+      <c r="G22" s="4"/>
+      <c r="H22" s="6">
         <v>27</v>
       </c>
-      <c r="I22" s="15">
+      <c r="I22" s="6">
         <v>11</v>
       </c>
-      <c r="J22" s="13">
+      <c r="J22" s="2">
         <v>2016</v>
       </c>
-      <c r="K22" s="9" t="s">
+      <c r="K22" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L22" s="9" t="s">
+      <c r="L22" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M22" s="8"/>
-      <c r="N22" s="9">
+      <c r="M22" s="5"/>
+      <c r="N22" s="5">
         <v>12</v>
       </c>
-      <c r="O22" s="9">
+      <c r="O22" s="5">
         <v>12</v>
       </c>
-      <c r="P22" s="9">
+      <c r="P22" s="5">
         <v>33</v>
       </c>
-      <c r="Q22" s="6" t="s">
+      <c r="Q22" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="R22" s="15" t="s">
+      <c r="R22" s="6" t="s">
         <v>106</v>
       </c>
-      <c r="S22" s="13">
+      <c r="S22" s="2">
         <v>19486376</v>
       </c>
-      <c r="T22" s="23">
+      <c r="T22" s="7">
         <v>4122496443</v>
       </c>
-      <c r="U22" s="13" t="s">
+      <c r="U22" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="V22" s="17" t="s">
+      <c r="V22" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="23" spans="1:26" ht="16.5">
-      <c r="A23" s="6">
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="13"/>
+      <c r="Z22" s="13"/>
+      <c r="AA22" s="13"/>
+      <c r="AB22" s="13"/>
+      <c r="AC22" s="13"/>
+      <c r="AD22" s="13"/>
+      <c r="AE22" s="13"/>
+    </row>
+    <row r="23" spans="1:31" ht="15.75">
+      <c r="A23" s="4">
         <v>13</v>
       </c>
-      <c r="B23" s="13">
+      <c r="B23" s="2">
         <v>11619892696</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="14" t="s">
+      <c r="C23" s="4"/>
+      <c r="D23" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="E23" s="14" t="s">
+      <c r="E23" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="F23" s="12" t="s">
+      <c r="F23" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G23" s="6"/>
-      <c r="H23" s="15">
+      <c r="G23" s="4"/>
+      <c r="H23" s="6">
         <v>15</v>
       </c>
-      <c r="I23" s="15">
+      <c r="I23" s="6">
         <v>3</v>
       </c>
-      <c r="J23" s="13">
+      <c r="J23" s="2">
         <v>2016</v>
       </c>
-      <c r="K23" s="9" t="s">
+      <c r="K23" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L23" s="9" t="s">
+      <c r="L23" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M23" s="8"/>
-      <c r="N23" s="9">
+      <c r="M23" s="5"/>
+      <c r="N23" s="5">
         <v>12</v>
       </c>
-      <c r="O23" s="9">
+      <c r="O23" s="5">
         <v>12</v>
       </c>
-      <c r="P23" s="9">
+      <c r="P23" s="5">
         <v>35</v>
       </c>
-      <c r="Q23" s="6" t="s">
+      <c r="Q23" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="R23" s="15" t="s">
+      <c r="R23" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="S23" s="13">
+      <c r="S23" s="2">
         <v>19892696</v>
       </c>
-      <c r="T23" s="13">
+      <c r="T23" s="2">
         <v>4121206878</v>
       </c>
-      <c r="U23" s="13" t="s">
+      <c r="U23" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="V23" s="17" t="s">
+      <c r="V23" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="24" spans="1:26" ht="16.5">
-      <c r="A24" s="6">
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="13"/>
+      <c r="Z23" s="13"/>
+      <c r="AA23" s="13"/>
+      <c r="AB23" s="13"/>
+      <c r="AC23" s="13"/>
+      <c r="AD23" s="13"/>
+      <c r="AE23" s="13"/>
+    </row>
+    <row r="24" spans="1:31" ht="15.75">
+      <c r="A24" s="4">
         <v>14</v>
       </c>
-      <c r="B24" s="13">
+      <c r="B24" s="2">
         <v>11620435077</v>
       </c>
-      <c r="C24" s="7"/>
-      <c r="D24" s="14" t="s">
+      <c r="C24" s="4"/>
+      <c r="D24" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="E24" s="14" t="s">
+      <c r="E24" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="F24" s="12" t="s">
+      <c r="F24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G24" s="6"/>
-      <c r="H24" s="15">
+      <c r="G24" s="4"/>
+      <c r="H24" s="6">
         <v>25</v>
       </c>
-      <c r="I24" s="21" t="s">
+      <c r="I24" s="8" t="s">
         <v>102</v>
       </c>
-      <c r="J24" s="13">
+      <c r="J24" s="2">
         <v>2016</v>
       </c>
-      <c r="K24" s="9" t="s">
+      <c r="K24" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L24" s="9" t="s">
+      <c r="L24" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M24" s="8"/>
-      <c r="N24" s="9">
+      <c r="M24" s="5"/>
+      <c r="N24" s="5">
         <v>12</v>
       </c>
-      <c r="O24" s="9">
+      <c r="O24" s="5">
         <v>12</v>
       </c>
-      <c r="P24" s="9">
+      <c r="P24" s="5">
         <v>35</v>
       </c>
-      <c r="Q24" s="6" t="s">
+      <c r="Q24" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="R24" s="15" t="s">
+      <c r="R24" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="S24" s="13">
+      <c r="S24" s="2">
         <v>20435077</v>
       </c>
-      <c r="T24" s="13">
+      <c r="T24" s="2">
         <v>4127641205</v>
       </c>
-      <c r="U24" s="13" t="s">
+      <c r="U24" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V24" s="17" t="s">
+      <c r="V24" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" ht="16.5">
-      <c r="A25" s="6">
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="13"/>
+      <c r="Z24" s="13"/>
+      <c r="AA24" s="13"/>
+      <c r="AB24" s="13"/>
+      <c r="AC24" s="13"/>
+      <c r="AD24" s="13"/>
+      <c r="AE24" s="13"/>
+    </row>
+    <row r="25" spans="1:31" ht="15.75">
+      <c r="A25" s="4">
         <v>15</v>
       </c>
-      <c r="B25" s="13">
+      <c r="B25" s="2">
         <v>11621121967</v>
       </c>
-      <c r="C25" s="7"/>
-      <c r="D25" s="14" t="s">
+      <c r="C25" s="4"/>
+      <c r="D25" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="E25" s="14" t="s">
+      <c r="E25" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="F25" s="12" t="s">
+      <c r="F25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="G25" s="6"/>
-      <c r="H25" s="22">
+      <c r="G25" s="4"/>
+      <c r="H25" s="9">
         <v>22</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I25" s="9">
         <v>10</v>
       </c>
-      <c r="J25" s="20">
+      <c r="J25" s="10">
         <v>2016</v>
       </c>
-      <c r="K25" s="9" t="s">
+      <c r="K25" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L25" s="9" t="s">
+      <c r="L25" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M25" s="8"/>
-      <c r="N25" s="9">
+      <c r="M25" s="5"/>
+      <c r="N25" s="5">
         <v>8</v>
       </c>
-      <c r="O25" s="9">
+      <c r="O25" s="5">
         <v>8</v>
       </c>
-      <c r="P25" s="9">
+      <c r="P25" s="5">
         <v>35</v>
       </c>
-      <c r="Q25" s="6" t="s">
+      <c r="Q25" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="R25" s="15" t="s">
+      <c r="R25" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="S25" s="13">
+      <c r="S25" s="2">
         <v>21121967</v>
       </c>
-      <c r="T25" s="13">
+      <c r="T25" s="2">
         <v>4164695815</v>
       </c>
-      <c r="U25" s="13" t="s">
+      <c r="U25" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V25" s="17" t="s">
+      <c r="V25" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="26" spans="1:26" ht="16.5">
-      <c r="A26" s="6">
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="13"/>
+      <c r="Z25" s="13"/>
+      <c r="AA25" s="13"/>
+      <c r="AB25" s="13"/>
+      <c r="AC25" s="13"/>
+      <c r="AD25" s="13"/>
+      <c r="AE25" s="13"/>
+    </row>
+    <row r="26" spans="1:31" ht="15.75">
+      <c r="A26" s="4">
         <v>16</v>
       </c>
-      <c r="B26" s="13">
+      <c r="B26" s="2">
         <v>11621182614</v>
       </c>
-      <c r="C26" s="7"/>
-      <c r="D26" s="14" t="s">
+      <c r="C26" s="4"/>
+      <c r="D26" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E26" s="14" t="s">
+      <c r="E26" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="F26" s="12" t="s">
+      <c r="F26" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="15">
+      <c r="G26" s="4"/>
+      <c r="H26" s="6">
         <v>15</v>
       </c>
-      <c r="I26" s="15">
+      <c r="I26" s="6">
         <v>9</v>
       </c>
-      <c r="J26" s="13">
+      <c r="J26" s="2">
         <v>2016</v>
       </c>
-      <c r="K26" s="9" t="s">
+      <c r="K26" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L26" s="9" t="s">
+      <c r="L26" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M26" s="8"/>
-      <c r="N26" s="9">
+      <c r="M26" s="5"/>
+      <c r="N26" s="5">
         <v>10</v>
       </c>
-      <c r="O26" s="9">
+      <c r="O26" s="5">
         <v>10</v>
       </c>
-      <c r="P26" s="9">
+      <c r="P26" s="5">
         <v>33</v>
       </c>
-      <c r="Q26" s="6" t="s">
+      <c r="Q26" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="R26" s="15" t="s">
+      <c r="R26" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="S26" s="13">
+      <c r="S26" s="2">
         <v>21182614</v>
       </c>
-      <c r="T26" s="13">
+      <c r="T26" s="2">
         <v>4269008536</v>
       </c>
-      <c r="U26" s="13" t="s">
+      <c r="U26" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="V26" s="17" t="s">
+      <c r="V26" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" ht="16.5">
-      <c r="A27" s="6">
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="13"/>
+      <c r="Z26" s="13"/>
+      <c r="AA26" s="13"/>
+      <c r="AB26" s="13"/>
+      <c r="AC26" s="13"/>
+      <c r="AD26" s="13"/>
+      <c r="AE26" s="13"/>
+    </row>
+    <row r="27" spans="1:31" ht="15.75">
+      <c r="A27" s="4">
         <v>17</v>
       </c>
-      <c r="B27" s="13">
+      <c r="B27" s="2">
         <v>11622655266</v>
       </c>
-      <c r="C27" s="7"/>
-      <c r="D27" s="14" t="s">
+      <c r="C27" s="4"/>
+      <c r="D27" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E27" s="14" t="s">
+      <c r="E27" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="F27" s="12" t="s">
+      <c r="F27" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G27" s="6"/>
-      <c r="H27" s="15">
+      <c r="G27" s="4"/>
+      <c r="H27" s="6">
         <v>23</v>
       </c>
-      <c r="I27" s="15">
+      <c r="I27" s="6">
         <v>8</v>
       </c>
-      <c r="J27" s="13">
+      <c r="J27" s="2">
         <v>2016</v>
       </c>
-      <c r="K27" s="9" t="s">
+      <c r="K27" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="L27" s="9" t="s">
+      <c r="L27" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M27" s="8"/>
-      <c r="N27" s="9">
+      <c r="M27" s="5"/>
+      <c r="N27" s="5">
         <v>12</v>
       </c>
-      <c r="O27" s="9">
+      <c r="O27" s="5">
         <v>12</v>
       </c>
-      <c r="P27" s="9">
+      <c r="P27" s="5">
         <v>34</v>
       </c>
-      <c r="Q27" s="6" t="s">
+      <c r="Q27" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="R27" s="15" t="s">
+      <c r="R27" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="S27" s="13">
+      <c r="S27" s="2">
         <v>22655266</v>
       </c>
-      <c r="T27" s="13">
+      <c r="T27" s="2">
         <v>4128095352</v>
       </c>
-      <c r="U27" s="13" t="s">
+      <c r="U27" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="V27" s="17" t="s">
+      <c r="V27" s="2" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="28" spans="1:26" ht="16.5">
-      <c r="A28" s="6">
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="13"/>
+      <c r="Z27" s="13"/>
+      <c r="AA27" s="13"/>
+      <c r="AB27" s="13"/>
+      <c r="AC27" s="13"/>
+      <c r="AD27" s="13"/>
+      <c r="AE27" s="13"/>
+    </row>
+    <row r="28" spans="1:31" ht="15.75">
+      <c r="A28" s="4">
         <v>18</v>
       </c>
-      <c r="B28" s="24">
+      <c r="B28" s="11">
         <v>11719486229</v>
       </c>
-      <c r="C28" s="7"/>
-      <c r="D28" s="25" t="s">
+      <c r="C28" s="4"/>
+      <c r="D28" s="12" t="s">
         <v>118</v>
       </c>
-      <c r="E28" s="14" t="s">
+      <c r="E28" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="F28" s="12" t="s">
+      <c r="F28" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="G28" s="6"/>
-      <c r="H28" s="15">
+      <c r="G28" s="4"/>
+      <c r="H28" s="6">
         <v>13</v>
       </c>
-      <c r="I28" s="15">
+      <c r="I28" s="6">
         <v>2</v>
       </c>
-      <c r="J28" s="13">
+      <c r="J28" s="2">
         <v>2017</v>
       </c>
-      <c r="K28" s="9" t="s">
+      <c r="K28" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="L28" s="9" t="s">
+      <c r="L28" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="M28" s="8"/>
-      <c r="N28" s="9">
+      <c r="M28" s="5"/>
+      <c r="N28" s="5">
         <v>10</v>
       </c>
-      <c r="O28" s="9">
+      <c r="O28" s="5">
         <v>10</v>
       </c>
-      <c r="P28" s="9">
+      <c r="P28" s="5">
         <v>31</v>
       </c>
-      <c r="Q28" s="6" t="s">
+      <c r="Q28" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="R28" s="6" t="s">
+      <c r="R28" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="S28" s="13">
+      <c r="S28" s="2">
         <v>19486229</v>
       </c>
-      <c r="T28" s="13">
+      <c r="T28" s="2">
         <v>4125496682</v>
       </c>
-      <c r="U28" s="13" t="s">
+      <c r="U28" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="V28" s="17" t="s">
+      <c r="V28" s="2" t="s">
         <v>55</v>
       </c>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="13"/>
+      <c r="Z28" s="13"/>
+      <c r="AA28" s="13"/>
+      <c r="AB28" s="13"/>
+      <c r="AC28" s="13"/>
+      <c r="AD28" s="13"/>
+      <c r="AE28" s="13"/>
+    </row>
+    <row r="29" spans="1:31" ht="15.75">
+      <c r="A29" s="13"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="13"/>
+      <c r="F29" s="13"/>
+      <c r="G29" s="13"/>
+      <c r="H29" s="13"/>
+      <c r="I29" s="13"/>
+      <c r="J29" s="13"/>
+      <c r="K29" s="13"/>
+      <c r="L29" s="13"/>
+      <c r="M29" s="13"/>
+      <c r="N29" s="13"/>
+      <c r="O29" s="13"/>
+      <c r="P29" s="13"/>
+      <c r="Q29" s="13"/>
+      <c r="R29" s="13"/>
+      <c r="S29" s="13"/>
+      <c r="T29" s="13"/>
+      <c r="U29" s="13"/>
+      <c r="V29" s="13"/>
+      <c r="W29" s="13"/>
+      <c r="X29" s="13"/>
+      <c r="Y29" s="13"/>
+      <c r="Z29" s="13"/>
+      <c r="AA29" s="13"/>
+      <c r="AB29" s="13"/>
+      <c r="AC29" s="13"/>
+      <c r="AD29" s="13"/>
+      <c r="AE29" s="13"/>
+    </row>
+    <row r="30" spans="1:31" ht="15.75">
+      <c r="A30" s="13"/>
+      <c r="B30" s="13"/>
+      <c r="C30" s="13"/>
+      <c r="D30" s="13"/>
+      <c r="E30" s="13"/>
+      <c r="F30" s="13"/>
+      <c r="G30" s="13"/>
+      <c r="H30" s="13"/>
+      <c r="I30" s="13"/>
+      <c r="J30" s="13"/>
+      <c r="K30" s="13"/>
+      <c r="L30" s="13"/>
+      <c r="M30" s="13"/>
+      <c r="N30" s="13"/>
+      <c r="O30" s="13"/>
+      <c r="P30" s="13"/>
+      <c r="Q30" s="13"/>
+      <c r="R30" s="13"/>
+      <c r="S30" s="13"/>
+      <c r="T30" s="13"/>
+      <c r="U30" s="13"/>
+      <c r="V30" s="13"/>
+      <c r="W30" s="13"/>
+      <c r="X30" s="13"/>
+      <c r="Y30" s="13"/>
+      <c r="Z30" s="13"/>
+      <c r="AA30" s="13"/>
+      <c r="AB30" s="13"/>
+      <c r="AC30" s="13"/>
+      <c r="AD30" s="13"/>
+      <c r="AE30" s="13"/>
+    </row>
+    <row r="31" spans="1:31" ht="15.75">
+      <c r="A31" s="13"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="13"/>
+      <c r="F31" s="13"/>
+      <c r="G31" s="13"/>
+      <c r="H31" s="13"/>
+      <c r="I31" s="13"/>
+      <c r="J31" s="13"/>
+      <c r="K31" s="13"/>
+      <c r="L31" s="13"/>
+      <c r="M31" s="13"/>
+      <c r="N31" s="13"/>
+      <c r="O31" s="13"/>
+      <c r="P31" s="13"/>
+      <c r="Q31" s="13"/>
+      <c r="R31" s="13"/>
+      <c r="S31" s="13"/>
+      <c r="T31" s="13"/>
+      <c r="U31" s="13"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13"/>
+      <c r="X31" s="13"/>
+      <c r="Y31" s="13"/>
+      <c r="Z31" s="13"/>
+      <c r="AA31" s="13"/>
+      <c r="AB31" s="13"/>
+      <c r="AC31" s="13"/>
+      <c r="AD31" s="13"/>
+      <c r="AE31" s="13"/>
+    </row>
+    <row r="32" spans="1:31" ht="15.75">
+      <c r="A32" s="13"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="13"/>
+      <c r="F32" s="13"/>
+      <c r="G32" s="13"/>
+      <c r="H32" s="13"/>
+      <c r="I32" s="13"/>
+      <c r="J32" s="13"/>
+      <c r="K32" s="13"/>
+      <c r="L32" s="13"/>
+      <c r="M32" s="13"/>
+      <c r="N32" s="13"/>
+      <c r="O32" s="13"/>
+      <c r="P32" s="13"/>
+      <c r="Q32" s="13"/>
+      <c r="R32" s="13"/>
+      <c r="S32" s="13"/>
+      <c r="T32" s="13"/>
+      <c r="U32" s="13"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13"/>
+      <c r="X32" s="13"/>
+      <c r="Y32" s="13"/>
+      <c r="Z32" s="13"/>
+      <c r="AA32" s="13"/>
+      <c r="AB32" s="13"/>
+      <c r="AC32" s="13"/>
+      <c r="AD32" s="13"/>
+      <c r="AE32" s="13"/>
+    </row>
+    <row r="33" spans="1:31" ht="15.75">
+      <c r="A33" s="13"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="13"/>
+      <c r="F33" s="13"/>
+      <c r="G33" s="13"/>
+      <c r="H33" s="13"/>
+      <c r="I33" s="13"/>
+      <c r="J33" s="13"/>
+      <c r="K33" s="13"/>
+      <c r="L33" s="13"/>
+      <c r="M33" s="13"/>
+      <c r="N33" s="13"/>
+      <c r="O33" s="13"/>
+      <c r="P33" s="13"/>
+      <c r="Q33" s="13"/>
+      <c r="R33" s="13"/>
+      <c r="S33" s="13"/>
+      <c r="T33" s="13"/>
+      <c r="U33" s="13"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="13"/>
+      <c r="Z33" s="13"/>
+      <c r="AA33" s="13"/>
+      <c r="AB33" s="13"/>
+      <c r="AC33" s="13"/>
+      <c r="AD33" s="13"/>
+      <c r="AE33" s="13"/>
+    </row>
+    <row r="34" spans="1:31" ht="15.75">
+      <c r="A34" s="13"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="13"/>
+      <c r="F34" s="13"/>
+      <c r="G34" s="13"/>
+      <c r="H34" s="13"/>
+      <c r="I34" s="13"/>
+      <c r="J34" s="13"/>
+      <c r="K34" s="13"/>
+      <c r="L34" s="13"/>
+      <c r="M34" s="13"/>
+      <c r="N34" s="13"/>
+      <c r="O34" s="13"/>
+      <c r="P34" s="13"/>
+      <c r="Q34" s="13"/>
+      <c r="R34" s="13"/>
+      <c r="S34" s="13"/>
+      <c r="T34" s="13"/>
+      <c r="U34" s="13"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
+      <c r="Y34" s="13"/>
+      <c r="Z34" s="13"/>
+      <c r="AA34" s="13"/>
+      <c r="AB34" s="13"/>
+      <c r="AC34" s="13"/>
+      <c r="AD34" s="13"/>
+      <c r="AE34" s="13"/>
+    </row>
+    <row r="35" spans="1:31" ht="15.75">
+      <c r="A35" s="13"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="13"/>
+      <c r="F35" s="13"/>
+      <c r="G35" s="13"/>
+      <c r="H35" s="13"/>
+      <c r="I35" s="13"/>
+      <c r="J35" s="13"/>
+      <c r="K35" s="13"/>
+      <c r="L35" s="13"/>
+      <c r="M35" s="13"/>
+      <c r="N35" s="13"/>
+      <c r="O35" s="13"/>
+      <c r="P35" s="13"/>
+      <c r="Q35" s="13"/>
+      <c r="R35" s="13"/>
+      <c r="S35" s="13"/>
+      <c r="T35" s="13"/>
+      <c r="U35" s="13"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="13"/>
+      <c r="Z35" s="13"/>
+      <c r="AA35" s="13"/>
+      <c r="AB35" s="13"/>
+      <c r="AC35" s="13"/>
+      <c r="AD35" s="13"/>
+      <c r="AE35" s="13"/>
+    </row>
+    <row r="36" spans="1:31" ht="15.75">
+      <c r="A36" s="13"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
+      <c r="K36" s="13"/>
+      <c r="L36" s="13"/>
+      <c r="M36" s="13"/>
+      <c r="N36" s="13"/>
+      <c r="O36" s="13"/>
+      <c r="P36" s="13"/>
+      <c r="Q36" s="13"/>
+      <c r="R36" s="13"/>
+      <c r="S36" s="13"/>
+      <c r="T36" s="13"/>
+      <c r="U36" s="13"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="13"/>
+      <c r="Z36" s="13"/>
+      <c r="AA36" s="13"/>
+      <c r="AB36" s="13"/>
+      <c r="AC36" s="13"/>
+      <c r="AD36" s="13"/>
+      <c r="AE36" s="13"/>
+    </row>
+    <row r="37" spans="1:31" ht="15.75">
+      <c r="A37" s="13"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="13"/>
+      <c r="F37" s="13"/>
+      <c r="G37" s="13"/>
+      <c r="H37" s="13"/>
+      <c r="I37" s="13"/>
+      <c r="J37" s="13"/>
+      <c r="K37" s="13"/>
+      <c r="L37" s="13"/>
+      <c r="M37" s="13"/>
+      <c r="N37" s="13"/>
+      <c r="O37" s="13"/>
+      <c r="P37" s="13"/>
+      <c r="Q37" s="13"/>
+      <c r="R37" s="13"/>
+      <c r="S37" s="13"/>
+      <c r="T37" s="13"/>
+      <c r="U37" s="13"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="13"/>
+      <c r="Z37" s="13"/>
+      <c r="AA37" s="13"/>
+      <c r="AB37" s="13"/>
+      <c r="AC37" s="13"/>
+      <c r="AD37" s="13"/>
+      <c r="AE37" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="40">
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="A5:V5"/>
-    <mergeCell ref="S6:V6"/>
-    <mergeCell ref="Q6:R6"/>
-    <mergeCell ref="M6:P6"/>
-    <mergeCell ref="I6:L6"/>
-    <mergeCell ref="E6:H6"/>
-    <mergeCell ref="W5:X5"/>
-    <mergeCell ref="Z5:AB5"/>
-    <mergeCell ref="AD5:AE5"/>
-    <mergeCell ref="W6:X6"/>
-    <mergeCell ref="Z6:AB6"/>
-    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="V9:V10"/>
+    <mergeCell ref="S9:S10"/>
+    <mergeCell ref="T9:T10"/>
+    <mergeCell ref="U9:U10"/>
+    <mergeCell ref="Q9:R10"/>
+    <mergeCell ref="D9:E10"/>
+    <mergeCell ref="H9:J9"/>
+    <mergeCell ref="L9:M9"/>
+    <mergeCell ref="N9:P9"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="B9:B10"/>
+    <mergeCell ref="C9:C10"/>
+    <mergeCell ref="F9:F10"/>
+    <mergeCell ref="G9:G10"/>
+    <mergeCell ref="K9:K10"/>
     <mergeCell ref="M7:N7"/>
     <mergeCell ref="O7:R7"/>
     <mergeCell ref="AB7:AD7"/>
@@ -2596,21 +3132,20 @@
     <mergeCell ref="F7:G7"/>
     <mergeCell ref="H7:J7"/>
     <mergeCell ref="K7:L7"/>
-    <mergeCell ref="D9:E10"/>
-    <mergeCell ref="H9:J9"/>
-    <mergeCell ref="L9:M9"/>
-    <mergeCell ref="N9:P9"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="B9:B10"/>
-    <mergeCell ref="C9:C10"/>
-    <mergeCell ref="F9:F10"/>
-    <mergeCell ref="G9:G10"/>
-    <mergeCell ref="K9:K10"/>
-    <mergeCell ref="V9:V10"/>
-    <mergeCell ref="S9:S10"/>
-    <mergeCell ref="T9:T10"/>
-    <mergeCell ref="U9:U10"/>
-    <mergeCell ref="Q9:R10"/>
+    <mergeCell ref="W5:X5"/>
+    <mergeCell ref="Z5:AB5"/>
+    <mergeCell ref="AD5:AE5"/>
+    <mergeCell ref="W6:X6"/>
+    <mergeCell ref="Z6:AB6"/>
+    <mergeCell ref="AD6:AE6"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A5:V5"/>
+    <mergeCell ref="S6:V6"/>
+    <mergeCell ref="Q6:R6"/>
+    <mergeCell ref="M6:P6"/>
+    <mergeCell ref="I6:L6"/>
+    <mergeCell ref="E6:H6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
